--- a/base_datas/media_uf_detalhamento.xlsx
+++ b/base_datas/media_uf_detalhamento.xlsx
@@ -603,22 +603,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>894.9689191433796</v>
+        <v>876.5423604713556</v>
       </c>
       <c r="C2">
-        <v>58.20024431209693</v>
+        <v>56.66313082260262</v>
       </c>
       <c r="D2">
-        <v>5144.03302271441</v>
+        <v>5124.781305943136</v>
       </c>
       <c r="E2">
-        <v>185.0769405388737</v>
+        <v>185.7896010865724</v>
       </c>
       <c r="F2">
-        <v>873.6929133176325</v>
+        <v>856.0111440881533</v>
       </c>
       <c r="G2">
-        <v>17.82620918628089</v>
+        <v>17.24569577418688</v>
       </c>
       <c r="H2">
         <v>34.49796639466256</v>
@@ -627,49 +627,49 @@
         <v>146.1711518736456</v>
       </c>
       <c r="J2">
-        <v>49.60194126070601</v>
+        <v>48.54251127406675</v>
       </c>
       <c r="K2">
         <v>-9.57655712571925E-15</v>
       </c>
       <c r="L2">
-        <v>2816.609895948105</v>
+        <v>2794.058130784711</v>
       </c>
       <c r="M2">
-        <v>801.0906826104025</v>
+        <v>799.6490042393393</v>
       </c>
       <c r="N2">
-        <v>1526.332444155902</v>
+        <v>1531.074170919086</v>
       </c>
       <c r="O2">
-        <v>155.2478704412039</v>
+        <v>157.3674683537052</v>
       </c>
       <c r="P2">
         <v>43.72352342891234</v>
       </c>
       <c r="S2">
-        <v>18.89818924044165</v>
+        <v>18.01177001169764</v>
       </c>
       <c r="T2">
-        <v>590.2526605040576</v>
+        <v>562.9087582637039</v>
       </c>
       <c r="U2">
-        <v>25.66244775348621</v>
+        <v>24.54888062381409</v>
       </c>
       <c r="V2">
-        <v>115.4932766648462</v>
+        <v>123.3107677592043</v>
       </c>
       <c r="W2">
-        <v>144.3648275101686</v>
+        <v>147.1179206813919</v>
       </c>
       <c r="Z2">
-        <v>0.6942080863176217</v>
+        <v>0.6479275472297826</v>
       </c>
       <c r="AA2">
-        <v>5.83325659217789</v>
+        <v>5.746747802236314</v>
       </c>
       <c r="AB2">
-        <v>13.32550288233666</v>
+        <v>12.70936354794536</v>
       </c>
       <c r="AC2">
         <v>4.558890560611722E-16</v>
@@ -678,43 +678,43 @@
         <v>34.49796639466256</v>
       </c>
       <c r="AH2">
-        <v>1327.005041802211</v>
+        <v>1327.782260252851</v>
       </c>
       <c r="AJ2">
-        <v>22.93279057850083</v>
+        <v>22.91025304797767</v>
       </c>
       <c r="AK2">
-        <v>727.6540774868911</v>
+        <v>717.7036738751575</v>
       </c>
       <c r="AL2">
-        <v>168.4318370655073</v>
+        <v>167.1381084222336</v>
       </c>
       <c r="AM2">
-        <v>276.5520292989233</v>
+        <v>273.8336859073697</v>
       </c>
       <c r="AN2">
-        <v>44.89368097454487</v>
+        <v>44.05505471853752</v>
       </c>
       <c r="AO2">
-        <v>249.140438741527</v>
+        <v>240.6350945605844</v>
       </c>
       <c r="AP2">
-        <v>673.4834610190576</v>
+        <v>672.9583883109318</v>
       </c>
       <c r="AQ2">
-        <v>50.4139133873451</v>
+        <v>49.64161879739414</v>
       </c>
       <c r="AR2">
-        <v>2.465137606402835</v>
+        <v>2.446170033455711</v>
       </c>
       <c r="AS2">
-        <v>5.722056927254454</v>
+        <v>5.848841720309421</v>
       </c>
       <c r="AT2">
         <v>0.04486931973408614</v>
       </c>
       <c r="AU2">
-        <v>71.99264517145608</v>
+        <v>71.63333694820435</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -727,70 +727,70 @@
         </is>
       </c>
       <c r="B3">
-        <v>469.9736510163895</v>
+        <v>466.8942213027942</v>
       </c>
       <c r="C3">
-        <v>252.2333172396661</v>
+        <v>255.6863463289083</v>
       </c>
       <c r="D3">
-        <v>8497.794316361009</v>
+        <v>8472.776612515148</v>
       </c>
       <c r="E3">
-        <v>308.5114343023655</v>
+        <v>307.106039354966</v>
       </c>
       <c r="F3">
-        <v>441.389286924589</v>
+        <v>437.7567841915504</v>
       </c>
       <c r="G3">
-        <v>25.03755974220178</v>
+        <v>24.83766146663136</v>
       </c>
       <c r="H3">
-        <v>57.34552562709868</v>
+        <v>62.94119455751184</v>
       </c>
       <c r="I3">
-        <v>201.6556388832431</v>
+        <v>206.6647815830364</v>
       </c>
       <c r="J3">
-        <v>108.7685701670524</v>
+        <v>108.1675501112556</v>
       </c>
       <c r="K3">
         <v>2.225093273152927E-15</v>
       </c>
       <c r="L3">
-        <v>5603.510163220668</v>
+        <v>5590.741487366864</v>
       </c>
       <c r="M3">
-        <v>1282.273452523542</v>
+        <v>1257.574557329721</v>
       </c>
       <c r="N3">
-        <v>1612.0107006168</v>
+        <v>1624.460567818564</v>
       </c>
       <c r="O3">
-        <v>241.2324670155197</v>
+        <v>238.0807899335536</v>
       </c>
       <c r="P3">
-        <v>70.20745227887586</v>
+        <v>75.37032068542781</v>
       </c>
       <c r="S3">
-        <v>48.96397973583473</v>
+        <v>48.97995136677738</v>
       </c>
       <c r="T3">
-        <v>49.81418581980702</v>
+        <v>49.8299688671674</v>
       </c>
       <c r="U3">
-        <v>27.26686643469086</v>
+        <v>26.78765709806783</v>
       </c>
       <c r="V3">
-        <v>177.6335143171896</v>
+        <v>174.5725157161971</v>
       </c>
       <c r="W3">
-        <v>179.8888200041839</v>
+        <v>179.8103594555492</v>
       </c>
       <c r="Z3">
-        <v>14.07320582535628</v>
+        <v>13.76633408350101</v>
       </c>
       <c r="AA3">
-        <v>20.31243502068962</v>
+        <v>20.1616882016007</v>
       </c>
       <c r="AB3">
         <v>9.223219405119215</v>
@@ -802,49 +802,49 @@
         <v>69.36389114743217</v>
       </c>
       <c r="AF3">
-        <v>106.0644104000054</v>
+        <v>105.076027067605</v>
       </c>
       <c r="AG3">
         <v>3.465389260560617</v>
       </c>
       <c r="AH3">
-        <v>2701.325272469679</v>
+        <v>2693.416892710382</v>
       </c>
       <c r="AJ3">
-        <v>304.9776563580851</v>
+        <v>302.2695651089113</v>
       </c>
       <c r="AK3">
-        <v>946.6766644709629</v>
+        <v>947.6196749545762</v>
       </c>
       <c r="AL3">
-        <v>200.826149297343</v>
+        <v>200.3189095461146</v>
       </c>
       <c r="AM3">
-        <v>1193.743020249705</v>
+        <v>1191.293643645422</v>
       </c>
       <c r="AN3">
-        <v>45.26075649540669</v>
+        <v>45.2561015581586</v>
       </c>
       <c r="AO3">
-        <v>217.330592930749</v>
+        <v>216.9979671860423</v>
       </c>
       <c r="AP3">
-        <v>1025.554099271947</v>
+        <v>1015.277078698776</v>
       </c>
       <c r="AQ3">
-        <v>63.3634633795448</v>
+        <v>63.32745802827179</v>
       </c>
       <c r="AR3">
-        <v>123.0385056335996</v>
+        <v>123.4072988095883</v>
       </c>
       <c r="AS3">
-        <v>8.273678364287726</v>
+        <v>8.152250690150469</v>
       </c>
       <c r="AT3">
-        <v>7.020164462480571</v>
+        <v>6.929330026770129</v>
       </c>
       <c r="AU3">
-        <v>98.8830627450921</v>
+        <v>84.89444681982658</v>
       </c>
       <c r="AV3">
         <v>1</v>
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>380.0789903829339</v>
+        <v>380.2774975941686</v>
       </c>
       <c r="C5">
-        <v>95.2729091053548</v>
+        <v>81.90731175722136</v>
       </c>
       <c r="D5">
-        <v>6826.507196228828</v>
+        <v>6549.730334661184</v>
       </c>
       <c r="E5">
-        <v>278.1818707328283</v>
+        <v>262.9728405558906</v>
       </c>
       <c r="F5">
-        <v>353.4808423584493</v>
+        <v>353.6990728787061</v>
       </c>
       <c r="G5">
-        <v>19.32795782244716</v>
+        <v>19.86596273596464</v>
       </c>
       <c r="H5">
         <v>18.97340507482217</v>
@@ -1005,49 +1005,49 @@
         <v>104.6739667449986</v>
       </c>
       <c r="J5">
-        <v>38.23539691303361</v>
+        <v>30.93106306411103</v>
       </c>
       <c r="K5">
         <v>-1.913493609694627E-14</v>
       </c>
       <c r="L5">
-        <v>3657.282603244038</v>
+        <v>3489.598997886615</v>
       </c>
       <c r="M5">
-        <v>1589.830202482057</v>
+        <v>1502.807821126866</v>
       </c>
       <c r="N5">
-        <v>1579.394390502732</v>
+        <v>1557.323515647703</v>
       </c>
       <c r="O5">
-        <v>244.4268370315762</v>
+        <v>231.6288806904423</v>
       </c>
       <c r="P5">
         <v>19.3318941806601</v>
       </c>
       <c r="S5">
-        <v>32.26796491812448</v>
+        <v>29.9631102811156</v>
       </c>
       <c r="T5">
         <v>8.360243086266131</v>
       </c>
       <c r="U5">
-        <v>4.331305241040625</v>
+        <v>4.156519773820636</v>
       </c>
       <c r="V5">
-        <v>209.2408152723003</v>
+        <v>210.9425768824639</v>
       </c>
       <c r="W5">
-        <v>135.4768295823071</v>
+        <v>134.4097396352975</v>
       </c>
       <c r="Z5">
-        <v>-3.507515107695887E-14</v>
+        <v>-3.258147573042344E-14</v>
       </c>
       <c r="AA5">
-        <v>12.67583155862383</v>
+        <v>11.79632011845678</v>
       </c>
       <c r="AB5">
-        <v>15.41689112075062</v>
+        <v>16.67166773515128</v>
       </c>
       <c r="AC5">
         <v>7.488114242259562E-16</v>
@@ -1059,40 +1059,40 @@
         <v>22.31710263983292</v>
       </c>
       <c r="AH5">
-        <v>1475.753466498959</v>
+        <v>1418.707443585861</v>
       </c>
       <c r="AJ5">
-        <v>207.3128435946604</v>
+        <v>193.3999196243371</v>
       </c>
       <c r="AK5">
-        <v>1081.142982164425</v>
+        <v>1033.528936172012</v>
       </c>
       <c r="AL5">
-        <v>122.6606480148862</v>
+        <v>121.5072407384194</v>
       </c>
       <c r="AM5">
-        <v>151.0833601573153</v>
+        <v>139.1972510173782</v>
       </c>
       <c r="AN5">
-        <v>43.93923592692951</v>
+        <v>42.37187426150076</v>
       </c>
       <c r="AO5">
-        <v>610.255457692397</v>
+        <v>570.714314847973</v>
       </c>
       <c r="AP5">
-        <v>1193.512142938834</v>
+        <v>1128.806746092135</v>
       </c>
       <c r="AQ5">
-        <v>25.15409138315029</v>
+        <v>25.27713785761071</v>
       </c>
       <c r="AR5">
-        <v>70.83186259035901</v>
+        <v>67.24551779400605</v>
       </c>
       <c r="AS5">
         <v>31.70429246990802</v>
       </c>
       <c r="AU5">
-        <v>278.9540013713575</v>
+        <v>261.371155142045</v>
       </c>
       <c r="AV5">
         <v>1</v>
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>479.9951160588133</v>
+        <v>482.9733592843909</v>
       </c>
       <c r="C6">
-        <v>61.66303521375799</v>
+        <v>62.04932474475883</v>
       </c>
       <c r="D6">
-        <v>6223.911268288663</v>
+        <v>6257.326465631653</v>
       </c>
       <c r="E6">
-        <v>158.4407086671033</v>
+        <v>158.6027426164357</v>
       </c>
       <c r="F6">
-        <v>441.7099515348201</v>
+        <v>444.4686762617119</v>
       </c>
       <c r="G6">
-        <v>36.98476428930296</v>
+        <v>37.19894510040362</v>
       </c>
       <c r="H6">
         <v>18.35858256263318</v>
@@ -1129,55 +1129,55 @@
         <v>206.7525909387922</v>
       </c>
       <c r="J6">
-        <v>36.60554045029787</v>
+        <v>36.80003587455943</v>
       </c>
       <c r="K6">
         <v>0.6996129452472266</v>
       </c>
       <c r="L6">
-        <v>4267.270060294652</v>
+        <v>4292.529737872541</v>
       </c>
       <c r="M6">
-        <v>842.4739198656512</v>
+        <v>850.4418926166944</v>
       </c>
       <c r="N6">
-        <v>1114.167288128358</v>
+        <v>1114.354835142418</v>
       </c>
       <c r="O6">
-        <v>94.2367340321332</v>
+        <v>94.15438820285902</v>
       </c>
       <c r="P6">
-        <v>55.57066003351745</v>
+        <v>56.3572401181045</v>
       </c>
       <c r="Q6">
         <v>2.890179627836936</v>
       </c>
       <c r="S6">
-        <v>40.82733965845946</v>
+        <v>41.03984394775974</v>
       </c>
       <c r="T6">
-        <v>37.05558044181533</v>
+        <v>37.88208295845894</v>
       </c>
       <c r="U6">
-        <v>31.14687603563921</v>
+        <v>31.74568156707896</v>
       </c>
       <c r="V6">
-        <v>194.1335105238184</v>
+        <v>195.5103320537838</v>
       </c>
       <c r="W6">
-        <v>179.5814449298117</v>
+        <v>179.5711630020682</v>
       </c>
       <c r="Z6">
         <v>2.503829583818792</v>
       </c>
       <c r="AA6">
-        <v>29.82321939936547</v>
+        <v>30.03268970081125</v>
       </c>
       <c r="AB6">
-        <v>10.22420829723585</v>
+        <v>10.21730357677953</v>
       </c>
       <c r="AC6">
-        <v>-3.258733423216428E-16</v>
+        <v>-3.384105404246196E-16</v>
       </c>
       <c r="AD6">
         <v>2.635221099284987</v>
@@ -1189,43 +1189,43 @@
         <v>4.621117106024005</v>
       </c>
       <c r="AH6">
-        <v>2242.514881929888</v>
+        <v>2264.157441600982</v>
       </c>
       <c r="AJ6">
-        <v>144.9631577614369</v>
+        <v>148.9185110680236</v>
       </c>
       <c r="AK6">
-        <v>673.7177190173793</v>
+        <v>674.0637860882964</v>
       </c>
       <c r="AL6">
-        <v>153.4777547723496</v>
+        <v>153.5926205057025</v>
       </c>
       <c r="AM6">
-        <v>929.2190268587008</v>
+        <v>927.7019384898114</v>
       </c>
       <c r="AN6">
-        <v>37.64761198677994</v>
+        <v>37.67201378970134</v>
       </c>
       <c r="AO6">
-        <v>86.53082221630774</v>
+        <v>87.24777285563972</v>
       </c>
       <c r="AP6">
-        <v>697.7292282670109</v>
+        <v>704.8662876283307</v>
       </c>
       <c r="AQ6">
-        <v>49.49618097168229</v>
+        <v>49.92574926351924</v>
       </c>
       <c r="AR6">
-        <v>36.77206252885046</v>
+        <v>36.87808961648097</v>
       </c>
       <c r="AS6">
-        <v>11.74390335340019</v>
+        <v>11.76541588175669</v>
       </c>
       <c r="AT6">
-        <v>18.91179797528065</v>
+        <v>19.22942541015036</v>
       </c>
       <c r="AU6">
-        <v>51.01705219217269</v>
+        <v>51.45370664622168</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1244,7 +1244,7 @@
         <v>121.3274378029106</v>
       </c>
       <c r="D7">
-        <v>6139.231718370922</v>
+        <v>6139.718650868513</v>
       </c>
       <c r="E7">
         <v>256.7116963755445</v>
@@ -1274,7 +1274,7 @@
         <v>925.9579679664495</v>
       </c>
       <c r="N7">
-        <v>992.7756751915193</v>
+        <v>993.2626076891092</v>
       </c>
       <c r="O7">
         <v>149.2937017078393</v>
@@ -1480,76 +1480,76 @@
         </is>
       </c>
       <c r="B9">
-        <v>790.6582087129118</v>
+        <v>792.1662574481028</v>
       </c>
       <c r="C9">
-        <v>158.5523726487649</v>
+        <v>158.3289823769555</v>
       </c>
       <c r="D9">
-        <v>6679.391789555311</v>
+        <v>6640.840049361908</v>
       </c>
       <c r="E9">
-        <v>535.0463308624343</v>
+        <v>533.2152555882357</v>
       </c>
       <c r="F9">
-        <v>718.9726079061346</v>
+        <v>720.5931715657259</v>
       </c>
       <c r="G9">
-        <v>69.5204831630213</v>
+        <v>69.43572615713052</v>
       </c>
       <c r="H9">
         <v>23.81629408131529</v>
       </c>
       <c r="I9">
-        <v>138.0646013358665</v>
+        <v>134.3828351875439</v>
       </c>
       <c r="J9">
-        <v>92.28136400754896</v>
+        <v>92.90575998301968</v>
       </c>
       <c r="K9">
-        <v>1.51147829263056E-15</v>
+        <v>2.890515813203534E-15</v>
       </c>
       <c r="L9">
-        <v>3304.469166646214</v>
+        <v>3282.128105532771</v>
       </c>
       <c r="M9">
-        <v>2230.641139396661</v>
+        <v>2215.623932984229</v>
       </c>
       <c r="N9">
-        <v>1144.281483512436</v>
+        <v>1143.088010844908</v>
       </c>
       <c r="O9">
-        <v>399.8448725706032</v>
+        <v>396.3803308125862</v>
       </c>
       <c r="P9">
-        <v>139.2252343043226</v>
+        <v>141.3989463342761</v>
       </c>
       <c r="Q9">
         <v>0.769951680159711</v>
       </c>
       <c r="S9">
-        <v>55.62418280156471</v>
+        <v>55.23886723202459</v>
       </c>
       <c r="T9">
-        <v>84.04584480010773</v>
+        <v>84.222061727312</v>
       </c>
       <c r="U9">
-        <v>60.56915600022906</v>
+        <v>60.60463125972671</v>
       </c>
       <c r="V9">
-        <v>389.3947761583281</v>
+        <v>391.4303335162501</v>
       </c>
       <c r="W9">
-        <v>184.9628309474697</v>
+        <v>184.3361450624371</v>
       </c>
       <c r="Z9">
-        <v>-6.34268656961232E-15</v>
+        <v>-6.687372127901107E-15</v>
       </c>
       <c r="AA9">
-        <v>24.07295335440537</v>
+        <v>23.98661980011252</v>
       </c>
       <c r="AB9">
-        <v>45.44752980861593</v>
+        <v>45.449106357018</v>
       </c>
       <c r="AC9">
         <v>-6.278861419867685E-16</v>
@@ -1567,43 +1567,43 @@
         <v>0.7783757766095443</v>
       </c>
       <c r="AH9">
-        <v>1871.305378133717</v>
+        <v>1858.380210295293</v>
       </c>
       <c r="AJ9">
-        <v>493.2086469041249</v>
+        <v>488.2417866996466</v>
       </c>
       <c r="AK9">
-        <v>594.2088750105023</v>
+        <v>591.5661045925568</v>
       </c>
       <c r="AL9">
-        <v>112.5080505617925</v>
+        <v>112.2666393267772</v>
       </c>
       <c r="AM9">
-        <v>150.4654640226338</v>
+        <v>149.4578242064039</v>
       </c>
       <c r="AN9">
-        <v>24.64645468572035</v>
+        <v>24.67924326922379</v>
       </c>
       <c r="AO9">
-        <v>60.720561917257</v>
+        <v>60.08522420370147</v>
       </c>
       <c r="AP9">
-        <v>1661.612062229777</v>
+        <v>1651.037575147466</v>
       </c>
       <c r="AQ9">
-        <v>164.3934601199574</v>
+        <v>164.1243929474149</v>
       </c>
       <c r="AR9">
-        <v>78.51936957770826</v>
+        <v>77.41380278520155</v>
       </c>
       <c r="AS9">
-        <v>42.52857461990821</v>
+        <v>42.17860669083768</v>
       </c>
       <c r="AT9">
-        <v>30.34252179816709</v>
+        <v>30.14143121513374</v>
       </c>
       <c r="AU9">
-        <v>273.2803898727461</v>
+        <v>270.2625288345934</v>
       </c>
       <c r="AV9">
         <v>1</v>
@@ -1616,46 +1616,46 @@
         </is>
       </c>
       <c r="B10">
-        <v>1049.144448435148</v>
+        <v>1039.316769418956</v>
       </c>
       <c r="C10">
-        <v>409.7967542722584</v>
+        <v>412.2567820252812</v>
       </c>
       <c r="D10">
-        <v>8625.410919898761</v>
+        <v>8654.701074828145</v>
       </c>
       <c r="E10">
-        <v>430.9408922170603</v>
+        <v>431.0839610918212</v>
       </c>
       <c r="F10">
-        <v>986.0954855359961</v>
+        <v>976.3806371192888</v>
       </c>
       <c r="G10">
-        <v>59.42296622465666</v>
+        <v>59.30873109488794</v>
       </c>
       <c r="H10">
         <v>55.94800459214945</v>
       </c>
       <c r="I10">
-        <v>448.0284494320294</v>
+        <v>448.1554310418101</v>
       </c>
       <c r="J10">
-        <v>63.75106344565983</v>
+        <v>63.94241783506438</v>
       </c>
       <c r="K10">
         <v>0.003813616686092018</v>
       </c>
       <c r="L10">
-        <v>5046.435505602432</v>
+        <v>5067.397330256596</v>
       </c>
       <c r="M10">
-        <v>2702.475648483372</v>
+        <v>2710.288161201808</v>
       </c>
       <c r="N10">
-        <v>876.4997658129571</v>
+        <v>877.0155833697406</v>
       </c>
       <c r="O10">
-        <v>293.7427468363926</v>
+        <v>293.8899699968011</v>
       </c>
       <c r="P10">
         <v>128.297009046822</v>
@@ -1667,28 +1667,28 @@
         <v>203.0695822454308</v>
       </c>
       <c r="S10">
-        <v>90.08850434898284</v>
+        <v>90.08435006333522</v>
       </c>
       <c r="T10">
-        <v>102.5978702832541</v>
+        <v>102.4013759066123</v>
       </c>
       <c r="U10">
-        <v>221.208280669138</v>
+        <v>221.1378608176974</v>
       </c>
       <c r="V10">
-        <v>427.7800852626311</v>
+        <v>418.2076498712406</v>
       </c>
       <c r="W10">
-        <v>239.6151266635368</v>
+        <v>239.7367905269326</v>
       </c>
       <c r="Z10">
         <v>1.755153244749021</v>
       </c>
       <c r="AA10">
-        <v>36.36790491329101</v>
+        <v>36.43590601576207</v>
       </c>
       <c r="AB10">
-        <v>34.2797098299915</v>
+        <v>34.24340078832319</v>
       </c>
       <c r="AC10">
         <v>-2.019169747409806E-15</v>
@@ -1706,43 +1706,43 @@
         <v>53.78938066054137</v>
       </c>
       <c r="AH10">
-        <v>3639.300559762842</v>
+        <v>3656.126721463409</v>
       </c>
       <c r="AJ10">
-        <v>220.3444655827873</v>
+        <v>216.4944029230494</v>
       </c>
       <c r="AK10">
-        <v>616.1131164216083</v>
+        <v>618.9551063176997</v>
       </c>
       <c r="AL10">
-        <v>99.16416880845948</v>
+        <v>99.2284070780986</v>
       </c>
       <c r="AM10">
-        <v>50.06964533972609</v>
+        <v>50.32326897428481</v>
       </c>
       <c r="AN10">
-        <v>49.65948560744007</v>
+        <v>49.83752518008421</v>
       </c>
       <c r="AO10">
-        <v>384.7022085587836</v>
+        <v>389.6178295036551</v>
       </c>
       <c r="AP10">
-        <v>2161.514190638619</v>
+        <v>2169.559165869844</v>
       </c>
       <c r="AQ10">
-        <v>173.986197156752</v>
+        <v>173.9947059497375</v>
       </c>
       <c r="AR10">
-        <v>81.93170741334393</v>
+        <v>81.9128302134512</v>
       </c>
       <c r="AS10">
-        <v>39.8645691473441</v>
+        <v>39.958757403516</v>
       </c>
       <c r="AT10">
         <v>58.36187574216106</v>
       </c>
       <c r="AU10">
-        <v>263.8686388997654</v>
+        <v>263.747461852849</v>
       </c>
       <c r="AV10">
         <v>1</v>
@@ -1755,22 +1755,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>318.7325877107284</v>
+        <v>318.521259280443</v>
       </c>
       <c r="C11">
         <v>99.58018862601645</v>
       </c>
       <c r="D11">
-        <v>6650.914866291366</v>
+        <v>6656.238925978912</v>
       </c>
       <c r="E11">
-        <v>134.4373418070505</v>
+        <v>134.3174283895547</v>
       </c>
       <c r="F11">
-        <v>293.0574037686495</v>
+        <v>292.9492474609598</v>
       </c>
       <c r="G11">
-        <v>23.29100169029511</v>
+        <v>23.18842537787995</v>
       </c>
       <c r="H11">
         <v>27.57386099503913</v>
@@ -1785,16 +1785,16 @@
         <v>0.1074401983122751</v>
       </c>
       <c r="L11">
-        <v>4769.201654290126</v>
+        <v>4774.865973346742</v>
       </c>
       <c r="M11">
-        <v>769.4104096926828</v>
+        <v>769.6370562008617</v>
       </c>
       <c r="N11">
-        <v>1112.302802308557</v>
+        <v>1111.735896431308</v>
       </c>
       <c r="O11">
-        <v>99.50527337437251</v>
+        <v>99.52315481542912</v>
       </c>
       <c r="P11">
         <v>43.24644508654328</v>
@@ -1803,28 +1803,28 @@
         <v>0.05101405951883867</v>
       </c>
       <c r="S11">
-        <v>20.40888915948232</v>
+        <v>20.33863131696107</v>
       </c>
       <c r="T11">
-        <v>7.05489594799883</v>
+        <v>7.02372136277474</v>
       </c>
       <c r="U11">
-        <v>16.61549882393017</v>
+        <v>16.59552090792729</v>
       </c>
       <c r="V11">
-        <v>122.7824398062903</v>
+        <v>122.9148989312726</v>
       </c>
       <c r="W11">
-        <v>147.1115992188831</v>
+        <v>146.9166435377674</v>
       </c>
       <c r="Z11">
-        <v>2.436851119263937</v>
+        <v>2.419568487212419</v>
       </c>
       <c r="AA11">
         <v>21.53980798000725</v>
       </c>
       <c r="AB11">
-        <v>10.08551793444234</v>
+        <v>10.03401659930062</v>
       </c>
       <c r="AC11">
         <v>7.683167832258924E-16</v>
@@ -1842,31 +1842,31 @@
         <v>8.791194982583958</v>
       </c>
       <c r="AH11">
-        <v>1914.565532397556</v>
+        <v>1916.907239000792</v>
       </c>
       <c r="AJ11">
-        <v>103.2032133339407</v>
+        <v>109.3722873166898</v>
       </c>
       <c r="AK11">
-        <v>830.6492503791078</v>
+        <v>829.1673939653311</v>
       </c>
       <c r="AL11">
-        <v>194.1622217705772</v>
+        <v>194.0001089097339</v>
       </c>
       <c r="AM11">
-        <v>1535.795672173236</v>
+        <v>1534.147161617151</v>
       </c>
       <c r="AN11">
-        <v>38.40382053523192</v>
+        <v>38.46809458243966</v>
       </c>
       <c r="AO11">
-        <v>152.4219437004756</v>
+        <v>152.8036879546037</v>
       </c>
       <c r="AP11">
-        <v>666.5532137744224</v>
+        <v>666.930664982128</v>
       </c>
       <c r="AQ11">
-        <v>39.95995900843643</v>
+        <v>40.06409561799442</v>
       </c>
       <c r="AR11">
         <v>44.54157107925538</v>
@@ -1878,7 +1878,7 @@
         <v>1.623434422464218</v>
       </c>
       <c r="AU11">
-        <v>42.59205918893312</v>
+        <v>42.43297512723149</v>
       </c>
       <c r="AV11">
         <v>1</v>
@@ -1891,49 +1891,49 @@
         </is>
       </c>
       <c r="B12">
-        <v>635.9576423575299</v>
+        <v>636.1019734491194</v>
       </c>
       <c r="C12">
-        <v>134.2013268511154</v>
+        <v>134.2236744739835</v>
       </c>
       <c r="D12">
-        <v>7421.00688504257</v>
+        <v>7419.737656659454</v>
       </c>
       <c r="E12">
-        <v>419.9405341995698</v>
+        <v>419.9879965064214</v>
       </c>
       <c r="F12">
-        <v>587.7017515407733</v>
+        <v>587.700718927465</v>
       </c>
       <c r="G12">
-        <v>48.57452415415532</v>
+        <v>48.66407122056039</v>
       </c>
       <c r="H12">
         <v>5.906751538980122</v>
       </c>
       <c r="I12">
-        <v>184.1910589354859</v>
+        <v>184.2848237783499</v>
       </c>
       <c r="J12">
-        <v>84.73251659398673</v>
+        <v>84.72948737748592</v>
       </c>
       <c r="K12">
         <v>1.202312530062143</v>
       </c>
       <c r="L12">
-        <v>4691.867807084325</v>
+        <v>4689.044019453602</v>
       </c>
       <c r="M12">
-        <v>1880.311934955559</v>
+        <v>1879.836437679636</v>
       </c>
       <c r="N12">
-        <v>851.0366752411767</v>
+        <v>850.8571995262148</v>
       </c>
       <c r="O12">
-        <v>297.8787973958964</v>
+        <v>297.9625267500586</v>
       </c>
       <c r="P12">
-        <v>108.0163551956808</v>
+        <v>108.2254113642338</v>
       </c>
       <c r="Q12">
         <v>2.143594943452089</v>
@@ -1942,28 +1942,28 @@
         <v>9.187907008118041</v>
       </c>
       <c r="S12">
-        <v>59.29358193895882</v>
+        <v>59.26362485220776</v>
       </c>
       <c r="T12">
-        <v>76.44506982475801</v>
+        <v>77.32442363994856</v>
       </c>
       <c r="U12">
-        <v>73.36738311409319</v>
+        <v>73.42560402527188</v>
       </c>
       <c r="V12">
-        <v>264.9974848137865</v>
+        <v>265.1431482737749</v>
       </c>
       <c r="W12">
-        <v>171.2375580277482</v>
+        <v>171.355940836935</v>
       </c>
       <c r="Z12">
-        <v>5.270332338473252</v>
+        <v>2.98419387534322</v>
       </c>
       <c r="AA12">
-        <v>20.88901255489865</v>
+        <v>20.89614167912072</v>
       </c>
       <c r="AB12">
-        <v>30.65609844531507</v>
+        <v>30.72723577724046</v>
       </c>
       <c r="AC12">
         <v>2.521289410518147E-17</v>
@@ -1981,43 +1981,43 @@
         <v>4.253247242372497</v>
       </c>
       <c r="AH12">
-        <v>3524.386772306313</v>
+        <v>3522.294153741738</v>
       </c>
       <c r="AJ12">
-        <v>254.0507675740037</v>
+        <v>253.8480592821876</v>
       </c>
       <c r="AK12">
-        <v>680.0702423364277</v>
+        <v>680.0712408508746</v>
       </c>
       <c r="AL12">
-        <v>81.93064380452589</v>
+        <v>81.90445319514635</v>
       </c>
       <c r="AM12">
-        <v>56.92835263920217</v>
+        <v>56.76151330054406</v>
       </c>
       <c r="AN12">
-        <v>36.16172790141364</v>
+        <v>36.09854410962389</v>
       </c>
       <c r="AO12">
-        <v>70.00518168784201</v>
+        <v>68.39837831933046</v>
       </c>
       <c r="AP12">
-        <v>1246.600262214744</v>
+        <v>1246.126706878465</v>
       </c>
       <c r="AQ12">
-        <v>195.739410788379</v>
+        <v>196.0154155260236</v>
       </c>
       <c r="AR12">
-        <v>267.3865082406565</v>
+        <v>267.3801775608055</v>
       </c>
       <c r="AS12">
-        <v>14.0125771381866</v>
+        <v>14.00519215672366</v>
       </c>
       <c r="AT12">
         <v>76.7955829353841</v>
       </c>
       <c r="AU12">
-        <v>149.4889290294792</v>
+        <v>149.2322731849108</v>
       </c>
       <c r="AV12">
         <v>1</v>
@@ -2084,19 +2084,19 @@
         <v>88.16812547500497</v>
       </c>
       <c r="T13">
-        <v>182.9200999503024</v>
+        <v>182.307777661898</v>
       </c>
       <c r="U13">
-        <v>342.4422335398873</v>
+        <v>342.4399174390605</v>
       </c>
       <c r="V13">
-        <v>545.4720827939356</v>
+        <v>545.4486344958082</v>
       </c>
       <c r="W13">
-        <v>369.4784555833429</v>
+        <v>370.1162161390691</v>
       </c>
       <c r="Z13">
-        <v>13.55570587872654</v>
+        <v>13.55570587872655</v>
       </c>
       <c r="AA13">
         <v>37.73029824460362</v>
@@ -2166,82 +2166,82 @@
         </is>
       </c>
       <c r="B14">
-        <v>1394.395683364409</v>
+        <v>1392.226961263706</v>
       </c>
       <c r="C14">
-        <v>298.3830888369537</v>
+        <v>297.3678536143105</v>
       </c>
       <c r="D14">
-        <v>9803.339120914075</v>
+        <v>9814.206060062555</v>
       </c>
       <c r="E14">
-        <v>540.5631098915642</v>
+        <v>538.8449909884678</v>
       </c>
       <c r="F14">
-        <v>1308.366447289934</v>
+        <v>1306.591571455213</v>
       </c>
       <c r="G14">
-        <v>79.9435492507365</v>
+        <v>79.54759545858333</v>
       </c>
       <c r="H14">
-        <v>21.60945136379287</v>
+        <v>21.89674323205076</v>
       </c>
       <c r="I14">
-        <v>267.7352360745447</v>
+        <v>266.2163498098935</v>
       </c>
       <c r="J14">
-        <v>94.62030381818064</v>
+        <v>94.5023270673733</v>
       </c>
       <c r="K14">
-        <v>8.253887993201079</v>
+        <v>8.036680414432629</v>
       </c>
       <c r="L14">
-        <v>3995.155849193381</v>
+        <v>4004.197898627362</v>
       </c>
       <c r="M14">
-        <v>4511.68493271653</v>
+        <v>4513.953304083222</v>
       </c>
       <c r="N14">
-        <v>1296.498339004165</v>
+        <v>1296.054857351973</v>
       </c>
       <c r="O14">
-        <v>339.0797619044193</v>
+        <v>339.2673753569248</v>
       </c>
       <c r="P14">
-        <v>122.9334257907968</v>
+        <v>120.7538243486655</v>
       </c>
       <c r="Q14">
         <v>1.085587067997094</v>
       </c>
       <c r="S14">
-        <v>103.8357983797181</v>
+        <v>103.3009675188097</v>
       </c>
       <c r="T14">
-        <v>165.1275984536931</v>
+        <v>163.9023286281575</v>
       </c>
       <c r="U14">
-        <v>311.0444595090846</v>
+        <v>311.3972113845477</v>
       </c>
       <c r="V14">
-        <v>477.8768701586687</v>
+        <v>479.224546748916</v>
       </c>
       <c r="W14">
-        <v>351.6153416875062</v>
+        <v>349.3892678443963</v>
       </c>
       <c r="Z14">
-        <v>8.54911689686357</v>
+        <v>8.477275578402528</v>
       </c>
       <c r="AA14">
-        <v>44.78986584591878</v>
+        <v>44.2425351455295</v>
       </c>
       <c r="AB14">
-        <v>36.56898569081153</v>
+        <v>36.69951727845041</v>
       </c>
       <c r="AC14">
-        <v>-5.140588069350847E-17</v>
+        <v>1.116450802501368E-16</v>
       </c>
       <c r="AD14">
-        <v>15.71861767645358</v>
+        <v>16.13469555462018</v>
       </c>
       <c r="AE14">
         <v>7.192318955928982</v>
@@ -2253,43 +2253,43 @@
         <v>0.2823638017250977</v>
       </c>
       <c r="AH14">
-        <v>2581.981615623111</v>
+        <v>2592.530395781424</v>
       </c>
       <c r="AJ14">
-        <v>145.5289301513234</v>
+        <v>144.9499524610576</v>
       </c>
       <c r="AK14">
-        <v>608.0545677318486</v>
+        <v>610.628327095541</v>
       </c>
       <c r="AL14">
-        <v>111.1414208628443</v>
+        <v>111.1185824621287</v>
       </c>
       <c r="AM14">
-        <v>60.28820769942612</v>
+        <v>60.08291450989151</v>
       </c>
       <c r="AN14">
-        <v>30.9574943881864</v>
+        <v>31.14671038059559</v>
       </c>
       <c r="AO14">
-        <v>464.5239716894279</v>
+        <v>460.932851752222</v>
       </c>
       <c r="AP14">
-        <v>3421.143945227376</v>
+        <v>3420.135016666493</v>
       </c>
       <c r="AQ14">
-        <v>211.0647547527794</v>
+        <v>210.5737899619185</v>
       </c>
       <c r="AR14">
-        <v>313.1197214053221</v>
+        <v>318.3983314428193</v>
       </c>
       <c r="AS14">
-        <v>11.4393156894799</v>
+        <v>11.5142820034529</v>
       </c>
       <c r="AT14">
-        <v>86.15095166396365</v>
+        <v>86.87674977613645</v>
       </c>
       <c r="AU14">
-        <v>520.5226103350665</v>
+        <v>518.6991563548953</v>
       </c>
       <c r="AV14">
         <v>1</v>
@@ -2302,76 +2302,76 @@
         </is>
       </c>
       <c r="B15">
-        <v>475.1053670414807</v>
+        <v>473.3028653390864</v>
       </c>
       <c r="C15">
-        <v>107.6486137744406</v>
+        <v>108.258172938994</v>
       </c>
       <c r="D15">
-        <v>6013.394005850463</v>
+        <v>6035.233105755449</v>
       </c>
       <c r="E15">
-        <v>140.0080824030472</v>
+        <v>138.3380154391594</v>
       </c>
       <c r="F15">
-        <v>436.3991994009299</v>
+        <v>435.4137291455066</v>
       </c>
       <c r="G15">
-        <v>33.50032345256311</v>
+        <v>32.88198834864507</v>
       </c>
       <c r="H15">
         <v>26.23745470745819</v>
       </c>
       <c r="I15">
-        <v>197.8987299971272</v>
+        <v>200.5276748368377</v>
       </c>
       <c r="J15">
-        <v>62.51381570492039</v>
+        <v>62.76029713567787</v>
       </c>
       <c r="K15">
-        <v>-7.08522302618731E-15</v>
+        <v>-7.120893416328675E-15</v>
       </c>
       <c r="L15">
-        <v>3883.476791521656</v>
+        <v>3897.811331621961</v>
       </c>
       <c r="M15">
-        <v>1089.028781592539</v>
+        <v>1088.785959622104</v>
       </c>
       <c r="N15">
-        <v>1040.888432736268</v>
+        <v>1048.635814511385</v>
       </c>
       <c r="O15">
-        <v>106.8244741268239</v>
+        <v>105.8110603281676</v>
       </c>
       <c r="P15">
-        <v>19.69092980349814</v>
+        <v>19.84973955381462</v>
       </c>
       <c r="S15">
-        <v>23.65069781579957</v>
+        <v>22.82937242821209</v>
       </c>
       <c r="T15">
-        <v>21.59153431203467</v>
+        <v>21.37363859645382</v>
       </c>
       <c r="U15">
-        <v>23.6502280061936</v>
+        <v>23.29328512963192</v>
       </c>
       <c r="V15">
-        <v>193.4033695304267</v>
+        <v>191.9667792202998</v>
       </c>
       <c r="W15">
-        <v>200.9788523917395</v>
+        <v>202.1810809460475</v>
       </c>
       <c r="Z15">
-        <v>0.06291593012461295</v>
+        <v>0.06136245036844901</v>
       </c>
       <c r="AA15">
-        <v>23.53587743080461</v>
+        <v>23.1961043169057</v>
       </c>
       <c r="AB15">
-        <v>12.98533712937002</v>
+        <v>12.62919441888897</v>
       </c>
       <c r="AC15">
-        <v>7.307972697119744E-16</v>
+        <v>7.287403217525325E-16</v>
       </c>
       <c r="AD15">
         <v>1.03155306216269</v>
@@ -2386,43 +2386,43 @@
         <v>5.013613556515284</v>
       </c>
       <c r="AH15">
-        <v>1414.311031845099</v>
+        <v>1406.4733558701</v>
       </c>
       <c r="AJ15">
-        <v>221.7006899327004</v>
+        <v>231.4439710940003</v>
       </c>
       <c r="AK15">
-        <v>720.7921937163848</v>
+        <v>715.5845318049729</v>
       </c>
       <c r="AL15">
-        <v>190.4414575044852</v>
+        <v>191.6580259577526</v>
       </c>
       <c r="AM15">
-        <v>1165.398330848308</v>
+        <v>1180.372259089934</v>
       </c>
       <c r="AN15">
-        <v>27.64933578343542</v>
+        <v>27.53041427309426</v>
       </c>
       <c r="AO15">
-        <v>152.6523841660987</v>
+        <v>153.9694046264806</v>
       </c>
       <c r="AP15">
-        <v>881.0289379879179</v>
+        <v>881.0601160675498</v>
       </c>
       <c r="AQ15">
-        <v>48.63499276498514</v>
+        <v>48.72836396249765</v>
       </c>
       <c r="AR15">
-        <v>32.38439920628989</v>
+        <v>32.22465026579661</v>
       </c>
       <c r="AS15">
-        <v>7.706429755282281</v>
+        <v>7.572948010799597</v>
       </c>
       <c r="AT15">
         <v>101.4534088611079</v>
       </c>
       <c r="AU15">
-        <v>116.8005401918979</v>
+        <v>117.3128144332659</v>
       </c>
       <c r="AV15">
         <v>1</v>
@@ -2435,46 +2435,46 @@
         </is>
       </c>
       <c r="B16">
-        <v>379.4155540238518</v>
+        <v>379.7486089622447</v>
       </c>
       <c r="C16">
-        <v>134.1544056181487</v>
+        <v>140.6526720018235</v>
       </c>
       <c r="D16">
-        <v>7748.627321036065</v>
+        <v>7784.377912004225</v>
       </c>
       <c r="E16">
-        <v>245.9490811746833</v>
+        <v>247.9120219212125</v>
       </c>
       <c r="F16">
-        <v>367.5497615346996</v>
+        <v>367.9377995511138</v>
       </c>
       <c r="G16">
-        <v>10.89874544438861</v>
+        <v>10.84473420849774</v>
       </c>
       <c r="H16">
         <v>45.18307473629735</v>
       </c>
       <c r="I16">
-        <v>207.1331987580212</v>
+        <v>223.2863218676609</v>
       </c>
       <c r="J16">
-        <v>46.66963840732476</v>
+        <v>46.54317744109431</v>
       </c>
       <c r="K16">
         <v>3.853790141072231</v>
       </c>
       <c r="L16">
-        <v>5655.750772645161</v>
+        <v>5675.976002873819</v>
       </c>
       <c r="M16">
-        <v>793.243764352591</v>
+        <v>805.048985690783</v>
       </c>
       <c r="N16">
-        <v>1299.632784038313</v>
+        <v>1303.352923439622</v>
       </c>
       <c r="O16">
-        <v>201.890044899241</v>
+        <v>203.7777217227271</v>
       </c>
       <c r="P16">
         <v>20.00849071406119</v>
@@ -2483,28 +2483,28 @@
         <v>33.71763317599461</v>
       </c>
       <c r="S16">
-        <v>40.10502816223625</v>
+        <v>40.19851332082404</v>
       </c>
       <c r="T16">
-        <v>17.61476387404759</v>
+        <v>17.63340161246707</v>
       </c>
       <c r="U16">
-        <v>14.57025360273143</v>
+        <v>14.45166123875386</v>
       </c>
       <c r="V16">
-        <v>140.1103401983291</v>
+        <v>139.8440399659864</v>
       </c>
       <c r="W16">
-        <v>196.9300969859272</v>
+        <v>197.7314997649434</v>
       </c>
       <c r="Z16">
-        <v>0.09454674044410333</v>
+        <v>0.0937717671617742</v>
       </c>
       <c r="AA16">
-        <v>7.066658456748383</v>
+        <v>7.017095929710732</v>
       </c>
       <c r="AB16">
-        <v>6.896860997656432</v>
+        <v>6.81050654127645</v>
       </c>
       <c r="AC16">
         <v>6.449656078781993E-17</v>
@@ -2516,43 +2516,43 @@
         <v>2.437539222821127</v>
       </c>
       <c r="AH16">
-        <v>3675.21750031994</v>
+        <v>3695.23122032374</v>
       </c>
       <c r="AJ16">
-        <v>82.61082638839591</v>
+        <v>82.87740025317493</v>
       </c>
       <c r="AK16">
-        <v>995.898068655364</v>
+        <v>995.6362520871581</v>
       </c>
       <c r="AL16">
-        <v>156.0597382561055</v>
+        <v>156.3554714512377</v>
       </c>
       <c r="AM16">
-        <v>573.606545293015</v>
+        <v>573.5745906321757</v>
       </c>
       <c r="AN16">
-        <v>67.7709779867744</v>
+        <v>67.61061304489429</v>
       </c>
       <c r="AO16">
-        <v>105.6657853324349</v>
+        <v>105.7658717337487</v>
       </c>
       <c r="AP16">
-        <v>676.2041743139666</v>
+        <v>687.8417579205335</v>
       </c>
       <c r="AQ16">
-        <v>38.3443248121819</v>
+        <v>38.26118191788368</v>
       </c>
       <c r="AR16">
-        <v>18.21096932871417</v>
+        <v>18.26430478079749</v>
       </c>
       <c r="AS16">
-        <v>7.488004740079988</v>
+        <v>7.54137914385418</v>
       </c>
       <c r="AT16">
         <v>45.62358850734597</v>
       </c>
       <c r="AU16">
-        <v>57.05262736568975</v>
+        <v>57.20406632301592</v>
       </c>
       <c r="AV16">
         <v>1</v>
@@ -2695,73 +2695,73 @@
         </is>
       </c>
       <c r="B18">
-        <v>429.6453507468882</v>
+        <v>428.9360747157584</v>
       </c>
       <c r="C18">
-        <v>126.3156274146282</v>
+        <v>125.5901701475724</v>
       </c>
       <c r="D18">
-        <v>7893.320919945343</v>
+        <v>7900.908570100449</v>
       </c>
       <c r="E18">
-        <v>210.1402185134369</v>
+        <v>210.9167592413834</v>
       </c>
       <c r="F18">
-        <v>418.4641140278596</v>
+        <v>417.7849539155561</v>
       </c>
       <c r="G18">
-        <v>10.65996334144459</v>
+        <v>10.75233069495926</v>
       </c>
       <c r="H18">
         <v>45.26523181662782</v>
       </c>
       <c r="I18">
-        <v>189.9203097340886</v>
+        <v>191.0183080356065</v>
       </c>
       <c r="J18">
-        <v>65.07225695793278</v>
+        <v>64.51600954687473</v>
       </c>
       <c r="K18">
         <v>0.07087164463178135</v>
       </c>
       <c r="L18">
-        <v>5742.425055580377</v>
+        <v>5743.714550276962</v>
       </c>
       <c r="M18">
-        <v>902.7702746776617</v>
+        <v>910.6865221124923</v>
       </c>
       <c r="N18">
-        <v>1248.125589687304</v>
+        <v>1246.507497710995</v>
       </c>
       <c r="O18">
-        <v>169.8343890796851</v>
+        <v>170.852885870101</v>
       </c>
       <c r="P18">
-        <v>26.23621485282043</v>
+        <v>28.33009556831703</v>
       </c>
       <c r="S18">
-        <v>35.39402665308685</v>
+        <v>34.75198045222304</v>
       </c>
       <c r="T18">
-        <v>8.957394090389529</v>
+        <v>8.824067396595133</v>
       </c>
       <c r="U18">
-        <v>13.63845131019322</v>
+        <v>13.58591608249533</v>
       </c>
       <c r="V18">
-        <v>200.1680049784581</v>
+        <v>201.9675143617488</v>
       </c>
       <c r="W18">
-        <v>196.3917901350173</v>
+        <v>194.1684450649516</v>
       </c>
       <c r="Z18">
-        <v>0.7742104280145806</v>
+        <v>0.7697759007229066</v>
       </c>
       <c r="AA18">
-        <v>7.137028385718112</v>
+        <v>7.060260112064665</v>
       </c>
       <c r="AB18">
-        <v>6.209808027191561</v>
+        <v>6.459946896146879</v>
       </c>
       <c r="AC18">
         <v>1.987432063814836E-16</v>
@@ -2776,43 +2776,43 @@
         <v>12.84229579139863</v>
       </c>
       <c r="AH18">
-        <v>3102.636923803904</v>
+        <v>3108.902964716199</v>
       </c>
       <c r="AJ18">
-        <v>58.34804118255609</v>
+        <v>58.31691938637424</v>
       </c>
       <c r="AK18">
-        <v>1055.280661545781</v>
+        <v>1055.976935304631</v>
       </c>
       <c r="AL18">
-        <v>187.8554097099199</v>
+        <v>187.31255113113</v>
       </c>
       <c r="AM18">
-        <v>1114.4423415445</v>
+        <v>1108.202636133514</v>
       </c>
       <c r="AN18">
-        <v>119.9686562983284</v>
+        <v>122.0806407828181</v>
       </c>
       <c r="AO18">
-        <v>104.7072529907342</v>
+        <v>103.7272490730512</v>
       </c>
       <c r="AP18">
-        <v>794.186663787202</v>
+        <v>801.9069587060185</v>
       </c>
       <c r="AQ18">
-        <v>39.75720581043812</v>
+        <v>39.77541708687345</v>
       </c>
       <c r="AR18">
-        <v>28.64960850468716</v>
+        <v>28.47045315206075</v>
       </c>
       <c r="AS18">
-        <v>6.990108591644944</v>
+        <v>6.908292160906424</v>
       </c>
       <c r="AT18">
         <v>0.492566705111465</v>
       </c>
       <c r="AU18">
-        <v>42.56256873981617</v>
+        <v>43.01416446960202</v>
       </c>
       <c r="AV18">
         <v>1</v>
@@ -2825,130 +2825,133 @@
         </is>
       </c>
       <c r="B19">
-        <v>976.0242920157862</v>
+        <v>964.054029083438</v>
       </c>
       <c r="C19">
-        <v>270.9515228021964</v>
+        <v>264.2437699172431</v>
       </c>
       <c r="D19">
-        <v>7492.955644707528</v>
+        <v>7531.667162058182</v>
       </c>
       <c r="E19">
-        <v>871.203589034183</v>
+        <v>877.6361149235962</v>
       </c>
       <c r="F19">
-        <v>873.8255846853172</v>
+        <v>870.0887962253997</v>
       </c>
       <c r="G19">
-        <v>94.24320197952296</v>
+        <v>92.22570790681783</v>
       </c>
       <c r="H19">
-        <v>25.66515204522582</v>
+        <v>5.631343486154424</v>
       </c>
       <c r="I19">
-        <v>375.8625181183115</v>
+        <v>364.9812246283638</v>
       </c>
       <c r="J19">
-        <v>100.9148117134511</v>
+        <v>101.3903264772311</v>
       </c>
       <c r="K19">
-        <v>8.94761162926909</v>
+        <v>4.29366546137942</v>
       </c>
       <c r="L19">
-        <v>4329.897670921562</v>
+        <v>4370.650923156331</v>
       </c>
       <c r="M19">
-        <v>2262.235294188189</v>
+        <v>2264.358395915931</v>
       </c>
       <c r="N19">
-        <v>900.8226795977768</v>
+        <v>896.657842985919</v>
       </c>
       <c r="O19">
-        <v>627.434018940983</v>
+        <v>623.5097857502074</v>
       </c>
       <c r="P19">
-        <v>138.1313082622489</v>
+        <v>150.2838500614095</v>
       </c>
       <c r="Q19">
-        <v>6.921312955641977</v>
+        <v>6.750146343515633</v>
       </c>
       <c r="R19">
         <v>1.041897762916584</v>
       </c>
       <c r="S19">
-        <v>130.7859342410308</v>
+        <v>131.5036161528378</v>
       </c>
       <c r="T19">
-        <v>179.9506410743442</v>
+        <v>179.0603276904858</v>
       </c>
       <c r="U19">
-        <v>129.0029670936583</v>
+        <v>128.992615684043</v>
       </c>
       <c r="V19">
-        <v>277.1246801823983</v>
+        <v>274.7602779552885</v>
       </c>
       <c r="W19">
-        <v>286.7111406459457</v>
+        <v>286.2692290526041</v>
       </c>
       <c r="Z19">
-        <v>1.937421613968987</v>
+        <v>1.887561498903609</v>
       </c>
       <c r="AA19">
-        <v>30.55513512454185</v>
+        <v>28.73987136289675</v>
       </c>
       <c r="AB19">
-        <v>65.16466540816378</v>
+        <v>64.90082446364411</v>
       </c>
       <c r="AC19">
-        <v>-1.067613514468407E-15</v>
+        <v>4.440056909738209E-17</v>
       </c>
       <c r="AD19">
-        <v>15.97727585174803</v>
+        <v>2.719436677613476</v>
+      </c>
+      <c r="AE19">
+        <v>9.70717674858223</v>
       </c>
       <c r="AF19">
         <v>13.47877030885351</v>
       </c>
       <c r="AG19">
-        <v>79.86686066667296</v>
+        <v>17.42802273315979</v>
       </c>
       <c r="AH19">
-        <v>3388.334067822414</v>
+        <v>3420.217523764472</v>
       </c>
       <c r="AJ19">
-        <v>100.7332056316056</v>
+        <v>103.910460294863</v>
       </c>
       <c r="AK19">
-        <v>435.6238176047293</v>
+        <v>434.7925094731169</v>
       </c>
       <c r="AL19">
-        <v>89.978431798671</v>
+        <v>90.82463506167618</v>
       </c>
       <c r="AM19">
-        <v>50.6593289244055</v>
+        <v>50.27267257888161</v>
       </c>
       <c r="AN19">
-        <v>34.15301745536157</v>
+        <v>34.19976279339867</v>
       </c>
       <c r="AO19">
-        <v>244.2911116575349</v>
+        <v>250.3285429778689</v>
       </c>
       <c r="AP19">
-        <v>1742.188091148902</v>
+        <v>1741.235515024803</v>
       </c>
       <c r="AQ19">
-        <v>226.7861354171087</v>
+        <v>225.5612832083159</v>
       </c>
       <c r="AR19">
-        <v>81.84302045990877</v>
+        <v>81.78504013388185</v>
       </c>
       <c r="AS19">
-        <v>60.42742990914245</v>
+        <v>60.2847516180231</v>
       </c>
       <c r="AT19">
-        <v>9.45701318928346</v>
+        <v>9.237490706711132</v>
       </c>
       <c r="AU19">
-        <v>167.7903642739971</v>
+        <v>172.3146822861723</v>
       </c>
       <c r="AV19">
         <v>1</v>
@@ -2961,28 +2964,28 @@
         </is>
       </c>
       <c r="B20">
-        <v>1302.528744808133</v>
+        <v>1315.705347105869</v>
       </c>
       <c r="C20">
-        <v>312.7202948024716</v>
+        <v>315.9147072211165</v>
       </c>
       <c r="D20">
-        <v>8542.324509769967</v>
+        <v>8546.03893076788</v>
       </c>
       <c r="E20">
-        <v>691.3150512194718</v>
+        <v>723.2332504640841</v>
       </c>
       <c r="F20">
-        <v>1218.16613498261</v>
+        <v>1230.890121205044</v>
       </c>
       <c r="G20">
-        <v>84.77310319762761</v>
+        <v>85.23110755953932</v>
       </c>
       <c r="H20">
         <v>16.62705552292083</v>
       </c>
       <c r="I20">
-        <v>264.8440938233483</v>
+        <v>264.89185477325</v>
       </c>
       <c r="J20">
         <v>87.58133598729383</v>
@@ -2991,19 +2994,19 @@
         <v>0.3407633428009137</v>
       </c>
       <c r="L20">
-        <v>5030.387783290327</v>
+        <v>5033.315515691625</v>
       </c>
       <c r="M20">
-        <v>2600.558162834371</v>
+        <v>2601.344851430987</v>
       </c>
       <c r="N20">
         <v>911.3785636452682</v>
       </c>
       <c r="O20">
-        <v>543.6396347054947</v>
+        <v>564.3915418577335</v>
       </c>
       <c r="P20">
-        <v>55.10586420646979</v>
+        <v>58.93441972944218</v>
       </c>
       <c r="Q20">
         <v>1.869257194710915</v>
@@ -3012,25 +3015,25 @@
         <v>0.4500406805860108</v>
       </c>
       <c r="S20">
-        <v>116.5295249870848</v>
+        <v>125.533809254721</v>
       </c>
       <c r="T20">
         <v>260.8298481635896</v>
       </c>
       <c r="U20">
-        <v>63.48807385412292</v>
+        <v>63.48824324996715</v>
       </c>
       <c r="V20">
-        <v>555.5508202274164</v>
+        <v>554.2037583135981</v>
       </c>
       <c r="W20">
-        <v>347.7003708979224</v>
+        <v>351.1447650368566</v>
       </c>
       <c r="Z20">
-        <v>1.650762658536451</v>
+        <v>1.624969491996817</v>
       </c>
       <c r="AA20">
-        <v>33.48138535230559</v>
+        <v>33.95056055231272</v>
       </c>
       <c r="AB20">
         <v>52.08889368704357</v>
@@ -3045,28 +3048,28 @@
         <v>9.326571642910727</v>
       </c>
       <c r="AH20">
-        <v>1273.463378525792</v>
+        <v>1273.367638524937</v>
       </c>
       <c r="AJ20">
-        <v>2640.199872326787</v>
+        <v>2640.169467348677</v>
       </c>
       <c r="AK20">
-        <v>852.9933709798016</v>
+        <v>846.0450091807576</v>
       </c>
       <c r="AL20">
-        <v>95.05639977349179</v>
+        <v>95.05572579226686</v>
       </c>
       <c r="AM20">
-        <v>36.9666722080155</v>
+        <v>36.93277410008073</v>
       </c>
       <c r="AN20">
         <v>17.35898704408823</v>
       </c>
       <c r="AO20">
-        <v>126.7365967963998</v>
+        <v>126.7365967306127</v>
       </c>
       <c r="AP20">
-        <v>1855.915637757537</v>
+        <v>1855.91555032649</v>
       </c>
       <c r="AQ20">
         <v>137.5848558477437</v>
@@ -3075,13 +3078,13 @@
         <v>149.4243403137135</v>
       </c>
       <c r="AS20">
-        <v>19.27028285513146</v>
+        <v>19.1796298637569</v>
       </c>
       <c r="AT20">
         <v>346.5683223979797</v>
       </c>
       <c r="AU20">
-        <v>125.017250061003</v>
+        <v>125.6477062601427</v>
       </c>
       <c r="AV20">
         <v>1</v>
@@ -3224,22 +3227,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>735.3055150006805</v>
+        <v>737.7889157029288</v>
       </c>
       <c r="C22">
-        <v>170.0816171519465</v>
+        <v>173.5014005714714</v>
       </c>
       <c r="D22">
-        <v>7074.101274406649</v>
+        <v>7028.590764592286</v>
       </c>
       <c r="E22">
-        <v>702.3866317830813</v>
+        <v>700.0411546514875</v>
       </c>
       <c r="F22">
-        <v>636.1082541038918</v>
+        <v>637.6769757419282</v>
       </c>
       <c r="G22">
-        <v>97.24737017016193</v>
+        <v>98.12381608287126</v>
       </c>
       <c r="H22">
         <v>20.27886355691953</v>
@@ -3248,52 +3251,52 @@
         <v>199.3410962151297</v>
       </c>
       <c r="J22">
-        <v>54.9112007990169</v>
+        <v>56.0260725267572</v>
       </c>
       <c r="K22">
         <v>3.643809541906234</v>
       </c>
       <c r="L22">
-        <v>3118.696785660024</v>
+        <v>3090.301067412581</v>
       </c>
       <c r="M22">
-        <v>2826.519117362694</v>
+        <v>2811.830530895172</v>
       </c>
       <c r="N22">
-        <v>1128.885371383932</v>
+        <v>1126.459166284534</v>
       </c>
       <c r="O22">
-        <v>616.2235557677528</v>
+        <v>612.7328956484231</v>
       </c>
       <c r="P22">
-        <v>56.70726118342905</v>
+        <v>58.53624533488201</v>
       </c>
       <c r="Q22">
         <v>0.008253024506255816</v>
       </c>
       <c r="S22">
-        <v>51.26614119043931</v>
+        <v>51.72724217157731</v>
       </c>
       <c r="T22">
-        <v>90.11703068245085</v>
+        <v>90.80547942802319</v>
       </c>
       <c r="U22">
-        <v>78.94122161162456</v>
+        <v>78.56350057518092</v>
       </c>
       <c r="V22">
-        <v>205.7243870562696</v>
+        <v>206.4421573477693</v>
       </c>
       <c r="W22">
-        <v>261.1749940655035</v>
+        <v>261.7122643560871</v>
       </c>
       <c r="Z22">
-        <v>0.2237793079500502</v>
+        <v>0.2303610523015193</v>
       </c>
       <c r="AA22">
-        <v>39.04091865516931</v>
+        <v>39.65363215010155</v>
       </c>
       <c r="AB22">
-        <v>64.39862720807693</v>
+        <v>64.82563870807076</v>
       </c>
       <c r="AC22">
         <v>-6.780048395757842E-16</v>
@@ -3308,43 +3311,43 @@
         <v>0.003866172025281671</v>
       </c>
       <c r="AH22">
-        <v>2020.530226206849</v>
+        <v>1993.461933718553</v>
       </c>
       <c r="AJ22">
-        <v>70.72421068193752</v>
+        <v>70.98041452584262</v>
       </c>
       <c r="AK22">
-        <v>727.4089620270735</v>
+        <v>723.435750770343</v>
       </c>
       <c r="AL22">
-        <v>97.20628525213442</v>
+        <v>97.19788777641067</v>
       </c>
       <c r="AM22">
-        <v>33.45768866685519</v>
+        <v>34.08011148289355</v>
       </c>
       <c r="AN22">
-        <v>29.53502989482972</v>
+        <v>29.30649972566236</v>
       </c>
       <c r="AO22">
-        <v>142.9005968878484</v>
+        <v>144.9924563520914</v>
       </c>
       <c r="AP22">
-        <v>2220.108124250088</v>
+        <v>2203.386024288404</v>
       </c>
       <c r="AQ22">
-        <v>155.8752219650086</v>
+        <v>158.2707718758985</v>
       </c>
       <c r="AR22">
-        <v>101.3360090896537</v>
+        <v>103.2414844899323</v>
       </c>
       <c r="AS22">
-        <v>15.85880390133695</v>
+        <v>15.07414512268055</v>
       </c>
       <c r="AT22">
         <v>8.307309736927188</v>
       </c>
       <c r="AU22">
-        <v>344.1304223055339</v>
+        <v>342.9690113702616</v>
       </c>
       <c r="AV22">
         <v>1</v>
@@ -3357,22 +3360,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>446.0969372552447</v>
+        <v>448.0110245262171</v>
       </c>
       <c r="C23">
         <v>55.02805657459191</v>
       </c>
       <c r="D23">
-        <v>5529.019267295256</v>
+        <v>5484.272843800647</v>
       </c>
       <c r="E23">
-        <v>210.6185484945813</v>
+        <v>203.7556245673298</v>
       </c>
       <c r="F23">
-        <v>425.5109191870501</v>
+        <v>428.2184211641384</v>
       </c>
       <c r="G23">
-        <v>12.97163407599636</v>
+        <v>12.68584496936034</v>
       </c>
       <c r="H23">
         <v>35.5337919635917</v>
@@ -3387,22 +3390,22 @@
         <v>-1.534692806646624E-14</v>
       </c>
       <c r="L23">
-        <v>2376.981280868997</v>
+        <v>2364.538151498577</v>
       </c>
       <c r="M23">
-        <v>1414.60821062782</v>
+        <v>1421.860888329588</v>
       </c>
       <c r="N23">
-        <v>1737.429775798439</v>
+        <v>1697.873803972481</v>
       </c>
       <c r="O23">
-        <v>187.8273661519494</v>
+        <v>180.1398701073066</v>
       </c>
       <c r="P23">
         <v>5.311899241145852</v>
       </c>
       <c r="S23">
-        <v>21.65291821952906</v>
+        <v>22.55337461179395</v>
       </c>
       <c r="T23">
         <v>28.22869560084434</v>
@@ -3411,16 +3414,16 @@
         <v>28.2061757746862</v>
       </c>
       <c r="V23">
-        <v>271.906414406621</v>
+        <v>276.0921946975892</v>
       </c>
       <c r="W23">
-        <v>111.2807640872981</v>
+        <v>112.6240684862937</v>
       </c>
       <c r="Z23">
         <v>-5.404360319086195E-15</v>
       </c>
       <c r="AA23">
-        <v>8.022424370274603</v>
+        <v>8.066582577353367</v>
       </c>
       <c r="AB23">
         <v>6.298994170918602</v>
@@ -3432,31 +3435,31 @@
         <v>35.5337919635917</v>
       </c>
       <c r="AH23">
-        <v>827.3215843223403</v>
+        <v>832.1582771525897</v>
       </c>
       <c r="AJ23">
-        <v>14.86381783488562</v>
+        <v>14.91657053574726</v>
       </c>
       <c r="AK23">
-        <v>927.2558737556816</v>
+        <v>939.6030134876868</v>
       </c>
       <c r="AL23">
-        <v>148.4808812787591</v>
+        <v>143.6661414138005</v>
       </c>
       <c r="AM23">
         <v>158.2912504035421</v>
       </c>
       <c r="AN23">
-        <v>44.89798885487215</v>
+        <v>47.3099964492415</v>
       </c>
       <c r="AO23">
-        <v>267.1764023048837</v>
+        <v>249.6984021097753</v>
       </c>
       <c r="AP23">
-        <v>994.9714693350694</v>
+        <v>1009.779811536662</v>
       </c>
       <c r="AQ23">
-        <v>24.82363208729171</v>
+        <v>24.27794140953907</v>
       </c>
       <c r="AR23">
         <v>36.27266159715779</v>
@@ -3465,7 +3468,7 @@
         <v>3.814679993240846</v>
       </c>
       <c r="AU23">
-        <v>357.9954933235524</v>
+        <v>353.4400272269403</v>
       </c>
       <c r="AV23">
         <v>1</v>
@@ -3478,49 +3481,49 @@
         </is>
       </c>
       <c r="B24">
-        <v>1031.579334734526</v>
+        <v>1033.363227642858</v>
       </c>
       <c r="C24">
-        <v>251.5318090091402</v>
+        <v>251.9620802040225</v>
       </c>
       <c r="D24">
-        <v>9101.414872766622</v>
+        <v>9116.559207688066</v>
       </c>
       <c r="E24">
-        <v>1082.15616296099</v>
+        <v>1083.832021098749</v>
       </c>
       <c r="F24">
-        <v>926.6947367746608</v>
+        <v>928.2868703506226</v>
       </c>
       <c r="G24">
-        <v>95.94402483147759</v>
+        <v>96.12192042368109</v>
       </c>
       <c r="H24">
-        <v>18.52819946791845</v>
+        <v>18.59640412797762</v>
       </c>
       <c r="I24">
-        <v>278.5506593136229</v>
+        <v>279.2530270394528</v>
       </c>
       <c r="J24">
-        <v>56.12057283233984</v>
+        <v>56.23644666367912</v>
       </c>
       <c r="K24">
         <v>1.860689247480703</v>
       </c>
       <c r="L24">
-        <v>5328.720622915509</v>
+        <v>5337.592997367003</v>
       </c>
       <c r="M24">
-        <v>2692.227802941826</v>
+        <v>2696.677290313875</v>
       </c>
       <c r="N24">
-        <v>1080.466446909286</v>
+        <v>1082.288920007187</v>
       </c>
       <c r="O24">
-        <v>874.7413454978166</v>
+        <v>876.0081428828692</v>
       </c>
       <c r="P24">
-        <v>114.0752077109033</v>
+        <v>114.3134919828136</v>
       </c>
       <c r="Q24">
         <v>14.93492419072816</v>
@@ -3529,34 +3532,34 @@
         <v>4.435880155336733</v>
       </c>
       <c r="S24">
-        <v>96.246302035764</v>
+        <v>96.43302743186986</v>
       </c>
       <c r="T24">
-        <v>220.6051723471401</v>
+        <v>221.0313601623224</v>
       </c>
       <c r="U24">
-        <v>118.6791181789837</v>
+        <v>118.8893962889143</v>
       </c>
       <c r="V24">
-        <v>286.59643872676</v>
+        <v>287.07874475446</v>
       </c>
       <c r="W24">
-        <v>295.660349998362</v>
+        <v>296.1345041381173</v>
       </c>
       <c r="Z24">
-        <v>11.53075280218674</v>
+        <v>11.58773583931933</v>
       </c>
       <c r="AA24">
-        <v>28.4164441912733</v>
+        <v>28.46217986391222</v>
       </c>
       <c r="AB24">
-        <v>68.5624820014032</v>
+        <v>68.69866256381442</v>
       </c>
       <c r="AC24">
         <v>1.19115358809284E-15</v>
       </c>
       <c r="AD24">
-        <v>19.03907345416913</v>
+        <v>19.12075350674383</v>
       </c>
       <c r="AE24">
         <v>1.135602582452303</v>
@@ -3568,34 +3571,34 @@
         <v>4.509747861230466</v>
       </c>
       <c r="AH24">
-        <v>4435.733093377401</v>
+        <v>4443.376474590589</v>
       </c>
       <c r="AJ24">
-        <v>122.6520830422104</v>
+        <v>122.8008065417082</v>
       </c>
       <c r="AK24">
-        <v>488.4039853057215</v>
+        <v>489.1654507719557</v>
       </c>
       <c r="AL24">
-        <v>94.83243992128801</v>
+        <v>95.00329164501369</v>
       </c>
       <c r="AM24">
-        <v>33.7382465974739</v>
+        <v>33.7608782218186</v>
       </c>
       <c r="AN24">
-        <v>42.38932308482197</v>
+        <v>42.46262170150149</v>
       </c>
       <c r="AO24">
-        <v>117.7642929183138</v>
+        <v>117.835477393663</v>
       </c>
       <c r="AP24">
-        <v>2082.635292275251</v>
+        <v>2086.049054126241</v>
       </c>
       <c r="AQ24">
-        <v>241.9699458424987</v>
+        <v>242.3729783622826</v>
       </c>
       <c r="AR24">
-        <v>145.5905592201943</v>
+        <v>145.8215855392816</v>
       </c>
       <c r="AS24">
         <v>15.34762460134454</v>
@@ -3604,7 +3607,7 @@
         <v>36.61616008435637</v>
       </c>
       <c r="AU24">
-        <v>218.7589938193743</v>
+        <v>219.1666377169457</v>
       </c>
       <c r="AV24">
         <v>1</v>
@@ -3617,22 +3620,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>1185.975139882347</v>
+        <v>1184.134297819028</v>
       </c>
       <c r="C25">
-        <v>165.3536995975672</v>
+        <v>165.0746345008095</v>
       </c>
       <c r="D25">
-        <v>8052.512660768194</v>
+        <v>8046.054103530919</v>
       </c>
       <c r="E25">
-        <v>628.2266148979086</v>
+        <v>626.6054700060693</v>
       </c>
       <c r="F25">
-        <v>1031.684811423651</v>
+        <v>1029.813166458684</v>
       </c>
       <c r="G25">
-        <v>149.667359376649</v>
+        <v>149.713940329771</v>
       </c>
       <c r="H25">
         <v>11.24922476631554</v>
@@ -3641,25 +3644,25 @@
         <v>284.5425322954725</v>
       </c>
       <c r="J25">
-        <v>87.78141138391265</v>
+        <v>87.77355057879316</v>
       </c>
       <c r="K25">
         <v>0.03262569226268733</v>
       </c>
       <c r="L25">
-        <v>3946.699950051145</v>
+        <v>3942.35997656567</v>
       </c>
       <c r="M25">
-        <v>2997.846412343469</v>
+        <v>2995.846747050983</v>
       </c>
       <c r="N25">
-        <v>1107.96629837358</v>
+        <v>1107.847379914266</v>
       </c>
       <c r="O25">
-        <v>423.7902834347027</v>
+        <v>422.7933795762269</v>
       </c>
       <c r="P25">
-        <v>132.3860006694533</v>
+        <v>131.880068509667</v>
       </c>
       <c r="Q25">
         <v>13.81041950298377</v>
@@ -3668,28 +3671,28 @@
         <v>18.52253699785579</v>
       </c>
       <c r="S25">
-        <v>83.5141908031876</v>
+        <v>83.3015007380657</v>
       </c>
       <c r="T25">
-        <v>203.2261135273958</v>
+        <v>202.887858995886</v>
       </c>
       <c r="U25">
-        <v>142.430404408459</v>
+        <v>142.1005846662375</v>
       </c>
       <c r="V25">
-        <v>377.7177322923181</v>
+        <v>377.038215543511</v>
       </c>
       <c r="W25">
-        <v>306.1574459287075</v>
+        <v>305.6384213327573</v>
       </c>
       <c r="Z25">
-        <v>4.838593222063728</v>
+        <v>4.815442058321796</v>
       </c>
       <c r="AA25">
-        <v>61.84616857746305</v>
+        <v>61.87217304459266</v>
       </c>
       <c r="AB25">
-        <v>89.35117670161077</v>
+        <v>89.36679796721268</v>
       </c>
       <c r="AC25">
         <v>5.56169388497354E-16</v>
@@ -3707,43 +3710,43 @@
         <v>6.250202025130831</v>
       </c>
       <c r="AH25">
-        <v>3076.223155479389</v>
+        <v>3071.865262624635</v>
       </c>
       <c r="AJ25">
-        <v>134.4843852240486</v>
+        <v>134.2920618085394</v>
       </c>
       <c r="AK25">
-        <v>470.5815193102653</v>
+        <v>470.7848577217045</v>
       </c>
       <c r="AL25">
-        <v>100.815466367737</v>
+        <v>100.846047675846</v>
       </c>
       <c r="AM25">
-        <v>43.83680646404046</v>
+        <v>43.99532599792018</v>
       </c>
       <c r="AN25">
-        <v>25.8769836765678</v>
+        <v>25.84772365500317</v>
       </c>
       <c r="AO25">
-        <v>101.0958001823152</v>
+        <v>100.9362003077183</v>
       </c>
       <c r="AP25">
-        <v>2446.704979485154</v>
+        <v>2444.117082995439</v>
       </c>
       <c r="AQ25">
-        <v>251.0161228042938</v>
+        <v>251.1967747682377</v>
       </c>
       <c r="AR25">
         <v>64.49406439242074</v>
       </c>
       <c r="AS25">
-        <v>23.45149507581805</v>
+        <v>23.41495980732754</v>
       </c>
       <c r="AT25">
         <v>100.4752440462378</v>
       </c>
       <c r="AU25">
-        <v>212.1841155378953</v>
+        <v>212.8458375279655</v>
       </c>
       <c r="AV25">
         <v>1</v>
@@ -3874,88 +3877,88 @@
         </is>
       </c>
       <c r="B27">
-        <v>1244.898524040178</v>
+        <v>1245.3730927943</v>
       </c>
       <c r="C27">
-        <v>181.0698426290762</v>
+        <v>181.549231006088</v>
       </c>
       <c r="D27">
-        <v>7319.693410738366</v>
+        <v>7316.662771343364</v>
       </c>
       <c r="E27">
-        <v>466.6588257423832</v>
+        <v>470.3852836293678</v>
       </c>
       <c r="F27">
-        <v>1146.277901053154</v>
+        <v>1146.768558356453</v>
       </c>
       <c r="G27">
-        <v>94.87679437346125</v>
+        <v>94.86617402099348</v>
       </c>
       <c r="H27">
-        <v>11.45817579663863</v>
+        <v>11.408633196749</v>
       </c>
       <c r="I27">
-        <v>246.3608178040394</v>
+        <v>246.7315119035978</v>
       </c>
       <c r="J27">
-        <v>67.35573116882203</v>
+        <v>67.40820812024289</v>
       </c>
       <c r="K27">
-        <v>3.598857806089743</v>
+        <v>3.578801804355434</v>
       </c>
       <c r="L27">
-        <v>3805.078020734939</v>
+        <v>3802.8211980764</v>
       </c>
       <c r="M27">
-        <v>2616.739727527851</v>
+        <v>2615.364891207917</v>
       </c>
       <c r="N27">
-        <v>903.513814202267</v>
+        <v>904.1097647051849</v>
       </c>
       <c r="O27">
-        <v>221.0422506187614</v>
+        <v>221.3776424039823</v>
       </c>
       <c r="P27">
-        <v>175.0872837220563</v>
+        <v>178.8571257904589</v>
       </c>
       <c r="Q27">
-        <v>4.344172116676698</v>
+        <v>4.121532129884597</v>
       </c>
       <c r="R27">
         <v>1.181639278571671</v>
       </c>
       <c r="S27">
-        <v>111.677181273829</v>
+        <v>112.1190767248769</v>
       </c>
       <c r="T27">
-        <v>328.659353635851</v>
+        <v>329.2061332748553</v>
       </c>
       <c r="U27">
-        <v>130.6201284162451</v>
+        <v>130.5296509255306</v>
       </c>
       <c r="V27">
-        <v>433.3149149886308</v>
+        <v>433.1600546107289</v>
       </c>
       <c r="W27">
-        <v>250.3859969833492</v>
+        <v>250.580839987946</v>
       </c>
       <c r="Z27">
-        <v>6.897887561756233</v>
+        <v>6.884388760265517</v>
       </c>
       <c r="AA27">
-        <v>36.84390563785018</v>
+        <v>36.90388055943028</v>
       </c>
       <c r="AB27">
-        <v>64.63179203119371</v>
+        <v>64.54770993811503</v>
       </c>
       <c r="AC27">
-        <v>1.940878656104455E-15</v>
+        <v>1.923245187466605E-15</v>
       </c>
       <c r="AD27">
         <v>1.665238684124251</v>
       </c>
       <c r="AE27">
-        <v>6.722916150199974</v>
+        <v>6.42696567163148</v>
       </c>
       <c r="AF27">
         <v>38.82408039984279</v>
@@ -3964,43 +3967,43 @@
         <v>3.106879656265534</v>
       </c>
       <c r="AH27">
-        <v>2998.851743120937</v>
+        <v>2996.402161720726</v>
       </c>
       <c r="AJ27">
-        <v>142.7605467522664</v>
+        <v>142.6297175059317</v>
       </c>
       <c r="AK27">
-        <v>439.8035641949485</v>
+        <v>440.2532770921396</v>
       </c>
       <c r="AL27">
-        <v>95.20716810786905</v>
+        <v>95.22992280181495</v>
       </c>
       <c r="AM27">
-        <v>23.95661283019205</v>
+        <v>23.9107063043517</v>
       </c>
       <c r="AN27">
         <v>25.68708160030294</v>
       </c>
       <c r="AO27">
-        <v>95.8134588256803</v>
+        <v>95.70747259112501</v>
       </c>
       <c r="AP27">
-        <v>1973.872967156138</v>
+        <v>1972.407713433833</v>
       </c>
       <c r="AQ27">
-        <v>276.5120476183987</v>
+        <v>276.6479607396732</v>
       </c>
       <c r="AR27">
-        <v>155.8442723102716</v>
+        <v>156.077922977693</v>
       </c>
       <c r="AS27">
-        <v>21.22963937358354</v>
+        <v>21.2224224585041</v>
       </c>
       <c r="AT27">
-        <v>12.39953680262162</v>
+        <v>12.37550527061049</v>
       </c>
       <c r="AU27">
-        <v>216.4061125885461</v>
+        <v>216.1333938911839</v>
       </c>
       <c r="AV27">
         <v>1</v>
@@ -4013,127 +4016,127 @@
         </is>
       </c>
       <c r="B28">
-        <v>574.5826298785489</v>
+        <v>590.1392828649523</v>
       </c>
       <c r="C28">
-        <v>111.4465119473491</v>
+        <v>128.6697474574575</v>
       </c>
       <c r="D28">
-        <v>8944.189999122507</v>
+        <v>9018.772719434084</v>
       </c>
       <c r="E28">
-        <v>222.3298463493575</v>
+        <v>225.8900962827426</v>
       </c>
       <c r="F28">
-        <v>549.8190856395711</v>
+        <v>565.0249303528935</v>
       </c>
       <c r="G28">
-        <v>23.18032951096759</v>
+        <v>23.36501801096198</v>
       </c>
       <c r="H28">
-        <v>19.4148161937559</v>
+        <v>20.45513201174031</v>
       </c>
       <c r="I28">
-        <v>189.4619670744927</v>
+        <v>218.7837798236315</v>
       </c>
       <c r="J28">
-        <v>36.99272281013427</v>
+        <v>37.4088882532572</v>
       </c>
       <c r="K28">
-        <v>5.938240872175045E-16</v>
+        <v>-2.032684762109858E-15</v>
       </c>
       <c r="L28">
-        <v>5410.532540475614</v>
+        <v>5487.877562300815</v>
       </c>
       <c r="M28">
-        <v>2024.349385696395</v>
+        <v>2014.89510838376</v>
       </c>
       <c r="N28">
-        <v>1509.3080729505</v>
+        <v>1516.000048749509</v>
       </c>
       <c r="O28">
-        <v>176.7440237823293</v>
+        <v>181.4743183838059</v>
       </c>
       <c r="P28">
-        <v>121.9699687481536</v>
+        <v>119.4817703363299</v>
       </c>
       <c r="Q28">
         <v>12.98147891380372</v>
       </c>
       <c r="S28">
-        <v>16.64739873202118</v>
+        <v>17.0953063803689</v>
       </c>
       <c r="T28">
-        <v>31.09801125573763</v>
+        <v>30.4193006503568</v>
       </c>
       <c r="U28">
-        <v>138.720797826301</v>
+        <v>149.1519420489016</v>
       </c>
       <c r="V28">
-        <v>240.9143864976693</v>
+        <v>247.8741477017943</v>
       </c>
       <c r="W28">
-        <v>142.622316941001</v>
+        <v>141.4994367350842</v>
       </c>
       <c r="Z28">
-        <v>1.43865203555422</v>
+        <v>1.388005391369795</v>
       </c>
       <c r="AA28">
-        <v>11.68583297042613</v>
+        <v>12.09641557148219</v>
       </c>
       <c r="AB28">
-        <v>13.40846870199749</v>
+        <v>13.05068008438368</v>
       </c>
       <c r="AC28">
-        <v>-1.877822842173898E-16</v>
+        <v>-7.264296627983323E-17</v>
       </c>
       <c r="AD28">
         <v>0.0008327328758771298</v>
       </c>
       <c r="AF28">
-        <v>21.76116461561307</v>
+        <v>22.94108926821906</v>
       </c>
       <c r="AG28">
         <v>9.90045019597234</v>
       </c>
       <c r="AH28">
-        <v>3744.676932244915</v>
+        <v>3789.809612653155</v>
       </c>
       <c r="AJ28">
-        <v>117.8920314325084</v>
+        <v>131.2836673204265</v>
       </c>
       <c r="AK28">
-        <v>1038.05974743105</v>
+        <v>1055.592282255554</v>
       </c>
       <c r="AL28">
-        <v>133.7038538435976</v>
+        <v>133.406045833899</v>
       </c>
       <c r="AM28">
-        <v>100.8427847720346</v>
+        <v>101.4933506620098</v>
       </c>
       <c r="AN28">
-        <v>56.59246246868586</v>
+        <v>56.97863551462265</v>
       </c>
       <c r="AO28">
-        <v>222.8640284768074</v>
+        <v>224.0217258212939</v>
       </c>
       <c r="AP28">
-        <v>1470.967783569237</v>
+        <v>1460.001717808222</v>
       </c>
       <c r="AQ28">
-        <v>96.58857595687546</v>
+        <v>95.99107076467398</v>
       </c>
       <c r="AR28">
-        <v>49.70543151065699</v>
+        <v>48.39329004880209</v>
       </c>
       <c r="AS28">
-        <v>8.822803441543471</v>
+        <v>8.907679221026751</v>
       </c>
       <c r="AT28">
         <v>46.91916992302737</v>
       </c>
       <c r="AU28">
-        <v>410.4816819067848</v>
+        <v>414.313043194131</v>
       </c>
       <c r="AV28">
         <v>1</v>

--- a/base_datas/media_uf_detalhamento.xlsx
+++ b/base_datas/media_uf_detalhamento.xlsx
@@ -603,22 +603,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>894.9689191433796</v>
+        <v>876.5423604713556</v>
       </c>
       <c r="C2">
-        <v>58.20024431209693</v>
+        <v>56.66313082260262</v>
       </c>
       <c r="D2">
-        <v>5144.03302271441</v>
+        <v>5124.781305943136</v>
       </c>
       <c r="E2">
-        <v>185.0769405388737</v>
+        <v>185.7896010865724</v>
       </c>
       <c r="F2">
-        <v>873.6929133176325</v>
+        <v>856.0111440881533</v>
       </c>
       <c r="G2">
-        <v>17.82620918628089</v>
+        <v>17.24569577418688</v>
       </c>
       <c r="H2">
         <v>34.49796639466256</v>
@@ -627,49 +627,49 @@
         <v>146.1711518736456</v>
       </c>
       <c r="J2">
-        <v>49.60194126070601</v>
+        <v>48.54251127406675</v>
       </c>
       <c r="K2">
         <v>-9.57655712571925E-15</v>
       </c>
       <c r="L2">
-        <v>2816.609895948105</v>
+        <v>2794.058130784711</v>
       </c>
       <c r="M2">
-        <v>801.0906826104025</v>
+        <v>799.6490042393393</v>
       </c>
       <c r="N2">
-        <v>1526.332444155902</v>
+        <v>1531.074170919086</v>
       </c>
       <c r="O2">
-        <v>155.2478704412039</v>
+        <v>157.3674683537052</v>
       </c>
       <c r="P2">
         <v>43.72352342891234</v>
       </c>
       <c r="S2">
-        <v>18.89818924044165</v>
+        <v>18.01177001169764</v>
       </c>
       <c r="T2">
-        <v>590.2526605040576</v>
+        <v>562.9087582637039</v>
       </c>
       <c r="U2">
-        <v>25.66244775348621</v>
+        <v>24.54888062381409</v>
       </c>
       <c r="V2">
-        <v>115.4932766648462</v>
+        <v>123.3107677592043</v>
       </c>
       <c r="W2">
-        <v>144.3648275101686</v>
+        <v>147.1179206813919</v>
       </c>
       <c r="Z2">
-        <v>0.6942080863176217</v>
+        <v>0.6479275472297826</v>
       </c>
       <c r="AA2">
-        <v>5.83325659217789</v>
+        <v>5.746747802236314</v>
       </c>
       <c r="AB2">
-        <v>13.32550288233666</v>
+        <v>12.70936354794536</v>
       </c>
       <c r="AC2">
         <v>4.558890560611722E-16</v>
@@ -678,43 +678,43 @@
         <v>34.49796639466256</v>
       </c>
       <c r="AH2">
-        <v>1327.005041802211</v>
+        <v>1327.782260252851</v>
       </c>
       <c r="AJ2">
-        <v>22.93279057850083</v>
+        <v>22.91025304797767</v>
       </c>
       <c r="AK2">
-        <v>727.6540774868911</v>
+        <v>717.7036738751575</v>
       </c>
       <c r="AL2">
-        <v>168.4318370655073</v>
+        <v>167.1381084222336</v>
       </c>
       <c r="AM2">
-        <v>276.5520292989233</v>
+        <v>273.8336859073697</v>
       </c>
       <c r="AN2">
-        <v>44.89368097454487</v>
+        <v>44.05505471853752</v>
       </c>
       <c r="AO2">
-        <v>249.140438741527</v>
+        <v>240.6350945605844</v>
       </c>
       <c r="AP2">
-        <v>673.4834610190576</v>
+        <v>672.9583883109318</v>
       </c>
       <c r="AQ2">
-        <v>50.4139133873451</v>
+        <v>49.64161879739414</v>
       </c>
       <c r="AR2">
-        <v>2.465137606402835</v>
+        <v>2.446170033455711</v>
       </c>
       <c r="AS2">
-        <v>5.722056927254454</v>
+        <v>5.848841720309421</v>
       </c>
       <c r="AT2">
         <v>0.04486931973408614</v>
       </c>
       <c r="AU2">
-        <v>71.99264517145608</v>
+        <v>71.63333694820435</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -727,70 +727,70 @@
         </is>
       </c>
       <c r="B3">
-        <v>469.9736510163895</v>
+        <v>466.8942213027942</v>
       </c>
       <c r="C3">
-        <v>252.2333172396661</v>
+        <v>255.6863463289083</v>
       </c>
       <c r="D3">
-        <v>8497.794316361009</v>
+        <v>8472.776612515148</v>
       </c>
       <c r="E3">
-        <v>308.5114343023655</v>
+        <v>307.106039354966</v>
       </c>
       <c r="F3">
-        <v>441.389286924589</v>
+        <v>437.7567841915504</v>
       </c>
       <c r="G3">
-        <v>25.03755974220178</v>
+        <v>24.83766146663136</v>
       </c>
       <c r="H3">
-        <v>57.34552562709868</v>
+        <v>62.94119455751184</v>
       </c>
       <c r="I3">
-        <v>201.6556388832431</v>
+        <v>206.6647815830364</v>
       </c>
       <c r="J3">
-        <v>108.7685701670524</v>
+        <v>108.1675501112556</v>
       </c>
       <c r="K3">
         <v>2.225093273152927E-15</v>
       </c>
       <c r="L3">
-        <v>5603.510163220668</v>
+        <v>5590.741487366864</v>
       </c>
       <c r="M3">
-        <v>1282.273452523542</v>
+        <v>1257.574557329721</v>
       </c>
       <c r="N3">
-        <v>1612.0107006168</v>
+        <v>1624.460567818564</v>
       </c>
       <c r="O3">
-        <v>241.2324670155197</v>
+        <v>238.0807899335536</v>
       </c>
       <c r="P3">
-        <v>70.20745227887586</v>
+        <v>75.37032068542781</v>
       </c>
       <c r="S3">
-        <v>48.96397973583473</v>
+        <v>48.97995136677738</v>
       </c>
       <c r="T3">
-        <v>49.81418581980702</v>
+        <v>49.8299688671674</v>
       </c>
       <c r="U3">
-        <v>27.26686643469086</v>
+        <v>26.78765709806783</v>
       </c>
       <c r="V3">
-        <v>177.6335143171896</v>
+        <v>174.5725157161971</v>
       </c>
       <c r="W3">
-        <v>179.8888200041839</v>
+        <v>179.8103594555492</v>
       </c>
       <c r="Z3">
-        <v>14.07320582535628</v>
+        <v>13.76633408350101</v>
       </c>
       <c r="AA3">
-        <v>20.31243502068962</v>
+        <v>20.1616882016007</v>
       </c>
       <c r="AB3">
         <v>9.223219405119215</v>
@@ -802,49 +802,49 @@
         <v>69.36389114743217</v>
       </c>
       <c r="AF3">
-        <v>106.0644104000054</v>
+        <v>105.076027067605</v>
       </c>
       <c r="AG3">
         <v>3.465389260560617</v>
       </c>
       <c r="AH3">
-        <v>2701.325272469679</v>
+        <v>2693.416892710382</v>
       </c>
       <c r="AJ3">
-        <v>304.9776563580851</v>
+        <v>302.2695651089113</v>
       </c>
       <c r="AK3">
-        <v>946.6766644709629</v>
+        <v>947.6196749545762</v>
       </c>
       <c r="AL3">
-        <v>200.826149297343</v>
+        <v>200.3189095461146</v>
       </c>
       <c r="AM3">
-        <v>1193.743020249705</v>
+        <v>1191.293643645422</v>
       </c>
       <c r="AN3">
-        <v>45.26075649540669</v>
+        <v>45.2561015581586</v>
       </c>
       <c r="AO3">
-        <v>217.330592930749</v>
+        <v>216.9979671860423</v>
       </c>
       <c r="AP3">
-        <v>1025.554099271947</v>
+        <v>1015.277078698776</v>
       </c>
       <c r="AQ3">
-        <v>63.3634633795448</v>
+        <v>63.32745802827179</v>
       </c>
       <c r="AR3">
-        <v>123.0385056335996</v>
+        <v>123.4072988095883</v>
       </c>
       <c r="AS3">
-        <v>8.273678364287726</v>
+        <v>8.152250690150469</v>
       </c>
       <c r="AT3">
-        <v>7.020164462480571</v>
+        <v>6.929330026770129</v>
       </c>
       <c r="AU3">
-        <v>98.8830627450921</v>
+        <v>84.89444681982658</v>
       </c>
       <c r="AV3">
         <v>1</v>
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>380.0789903829339</v>
+        <v>380.2774975941686</v>
       </c>
       <c r="C5">
-        <v>95.2729091053548</v>
+        <v>81.90731175722136</v>
       </c>
       <c r="D5">
-        <v>6826.507196228828</v>
+        <v>6549.730334661184</v>
       </c>
       <c r="E5">
-        <v>278.1818707328283</v>
+        <v>262.9728405558906</v>
       </c>
       <c r="F5">
-        <v>353.4808423584493</v>
+        <v>353.6990728787061</v>
       </c>
       <c r="G5">
-        <v>19.32795782244716</v>
+        <v>19.86596273596464</v>
       </c>
       <c r="H5">
         <v>18.97340507482217</v>
@@ -1005,49 +1005,49 @@
         <v>104.6739667449986</v>
       </c>
       <c r="J5">
-        <v>38.23539691303361</v>
+        <v>30.93106306411103</v>
       </c>
       <c r="K5">
         <v>-1.913493609694627E-14</v>
       </c>
       <c r="L5">
-        <v>3657.282603244038</v>
+        <v>3489.598997886615</v>
       </c>
       <c r="M5">
-        <v>1589.830202482057</v>
+        <v>1502.807821126866</v>
       </c>
       <c r="N5">
-        <v>1579.394390502732</v>
+        <v>1557.323515647703</v>
       </c>
       <c r="O5">
-        <v>244.4268370315762</v>
+        <v>231.6288806904423</v>
       </c>
       <c r="P5">
         <v>19.3318941806601</v>
       </c>
       <c r="S5">
-        <v>32.26796491812448</v>
+        <v>29.9631102811156</v>
       </c>
       <c r="T5">
         <v>8.360243086266131</v>
       </c>
       <c r="U5">
-        <v>4.331305241040625</v>
+        <v>4.156519773820636</v>
       </c>
       <c r="V5">
-        <v>209.2408152723003</v>
+        <v>210.9425768824639</v>
       </c>
       <c r="W5">
-        <v>135.4768295823071</v>
+        <v>134.4097396352975</v>
       </c>
       <c r="Z5">
-        <v>-3.507515107695887E-14</v>
+        <v>-3.258147573042344E-14</v>
       </c>
       <c r="AA5">
-        <v>12.67583155862383</v>
+        <v>11.79632011845678</v>
       </c>
       <c r="AB5">
-        <v>15.41689112075062</v>
+        <v>16.67166773515128</v>
       </c>
       <c r="AC5">
         <v>7.488114242259562E-16</v>
@@ -1059,40 +1059,40 @@
         <v>22.31710263983292</v>
       </c>
       <c r="AH5">
-        <v>1475.753466498959</v>
+        <v>1418.707443585861</v>
       </c>
       <c r="AJ5">
-        <v>207.3128435946604</v>
+        <v>193.3999196243371</v>
       </c>
       <c r="AK5">
-        <v>1081.142982164425</v>
+        <v>1033.528936172012</v>
       </c>
       <c r="AL5">
-        <v>122.6606480148862</v>
+        <v>121.5072407384194</v>
       </c>
       <c r="AM5">
-        <v>151.0833601573153</v>
+        <v>139.1972510173782</v>
       </c>
       <c r="AN5">
-        <v>43.93923592692951</v>
+        <v>42.37187426150076</v>
       </c>
       <c r="AO5">
-        <v>610.255457692397</v>
+        <v>570.714314847973</v>
       </c>
       <c r="AP5">
-        <v>1193.512142938834</v>
+        <v>1128.806746092135</v>
       </c>
       <c r="AQ5">
-        <v>25.15409138315029</v>
+        <v>25.27713785761071</v>
       </c>
       <c r="AR5">
-        <v>70.83186259035901</v>
+        <v>67.24551779400605</v>
       </c>
       <c r="AS5">
         <v>31.70429246990802</v>
       </c>
       <c r="AU5">
-        <v>278.9540013713575</v>
+        <v>261.371155142045</v>
       </c>
       <c r="AV5">
         <v>1</v>
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>479.9951160588133</v>
+        <v>482.9733592843909</v>
       </c>
       <c r="C6">
-        <v>61.66303521375799</v>
+        <v>62.04932474475883</v>
       </c>
       <c r="D6">
-        <v>6223.911268288663</v>
+        <v>6257.326465631653</v>
       </c>
       <c r="E6">
-        <v>158.4407086671033</v>
+        <v>158.6027426164357</v>
       </c>
       <c r="F6">
-        <v>441.7099515348201</v>
+        <v>444.4686762617119</v>
       </c>
       <c r="G6">
-        <v>36.98476428930296</v>
+        <v>37.19894510040362</v>
       </c>
       <c r="H6">
         <v>18.35858256263318</v>
@@ -1129,55 +1129,55 @@
         <v>206.7525909387922</v>
       </c>
       <c r="J6">
-        <v>36.60554045029787</v>
+        <v>36.80003587455943</v>
       </c>
       <c r="K6">
         <v>0.6996129452472266</v>
       </c>
       <c r="L6">
-        <v>4267.270060294652</v>
+        <v>4292.529737872541</v>
       </c>
       <c r="M6">
-        <v>842.4739198656512</v>
+        <v>850.4418926166944</v>
       </c>
       <c r="N6">
-        <v>1114.167288128358</v>
+        <v>1114.354835142418</v>
       </c>
       <c r="O6">
-        <v>94.2367340321332</v>
+        <v>94.15438820285902</v>
       </c>
       <c r="P6">
-        <v>55.57066003351745</v>
+        <v>56.3572401181045</v>
       </c>
       <c r="Q6">
         <v>2.890179627836936</v>
       </c>
       <c r="S6">
-        <v>40.82733965845946</v>
+        <v>41.03984394775974</v>
       </c>
       <c r="T6">
-        <v>37.05558044181533</v>
+        <v>37.88208295845894</v>
       </c>
       <c r="U6">
-        <v>31.14687603563921</v>
+        <v>31.74568156707896</v>
       </c>
       <c r="V6">
-        <v>194.1335105238184</v>
+        <v>195.5103320537838</v>
       </c>
       <c r="W6">
-        <v>179.5814449298117</v>
+        <v>179.5711630020682</v>
       </c>
       <c r="Z6">
         <v>2.503829583818792</v>
       </c>
       <c r="AA6">
-        <v>29.82321939936547</v>
+        <v>30.03268970081125</v>
       </c>
       <c r="AB6">
-        <v>10.22420829723585</v>
+        <v>10.21730357677953</v>
       </c>
       <c r="AC6">
-        <v>-3.258733423216428E-16</v>
+        <v>-3.384105404246196E-16</v>
       </c>
       <c r="AD6">
         <v>2.635221099284987</v>
@@ -1189,43 +1189,43 @@
         <v>4.621117106024005</v>
       </c>
       <c r="AH6">
-        <v>2242.514881929888</v>
+        <v>2264.157441600982</v>
       </c>
       <c r="AJ6">
-        <v>144.9631577614369</v>
+        <v>148.9185110680236</v>
       </c>
       <c r="AK6">
-        <v>673.7177190173793</v>
+        <v>674.0637860882964</v>
       </c>
       <c r="AL6">
-        <v>153.4777547723496</v>
+        <v>153.5926205057025</v>
       </c>
       <c r="AM6">
-        <v>929.2190268587008</v>
+        <v>927.7019384898114</v>
       </c>
       <c r="AN6">
-        <v>37.64761198677994</v>
+        <v>37.67201378970134</v>
       </c>
       <c r="AO6">
-        <v>86.53082221630774</v>
+        <v>87.24777285563972</v>
       </c>
       <c r="AP6">
-        <v>697.7292282670109</v>
+        <v>704.8662876283307</v>
       </c>
       <c r="AQ6">
-        <v>49.49618097168229</v>
+        <v>49.92574926351924</v>
       </c>
       <c r="AR6">
-        <v>36.77206252885046</v>
+        <v>36.87808961648097</v>
       </c>
       <c r="AS6">
-        <v>11.74390335340019</v>
+        <v>11.76541588175669</v>
       </c>
       <c r="AT6">
-        <v>18.91179797528065</v>
+        <v>19.22942541015036</v>
       </c>
       <c r="AU6">
-        <v>51.01705219217269</v>
+        <v>51.45370664622168</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1244,7 +1244,7 @@
         <v>121.3274378029106</v>
       </c>
       <c r="D7">
-        <v>6139.231718370922</v>
+        <v>6139.718650868513</v>
       </c>
       <c r="E7">
         <v>256.7116963755445</v>
@@ -1274,7 +1274,7 @@
         <v>925.9579679664495</v>
       </c>
       <c r="N7">
-        <v>992.7756751915193</v>
+        <v>993.2626076891092</v>
       </c>
       <c r="O7">
         <v>149.2937017078393</v>
@@ -1480,76 +1480,76 @@
         </is>
       </c>
       <c r="B9">
-        <v>790.6582087129118</v>
+        <v>792.1662574481028</v>
       </c>
       <c r="C9">
-        <v>158.5523726487649</v>
+        <v>158.3289823769555</v>
       </c>
       <c r="D9">
-        <v>6679.391789555311</v>
+        <v>6640.840049361908</v>
       </c>
       <c r="E9">
-        <v>535.0463308624343</v>
+        <v>533.2152555882357</v>
       </c>
       <c r="F9">
-        <v>718.9726079061346</v>
+        <v>720.5931715657259</v>
       </c>
       <c r="G9">
-        <v>69.5204831630213</v>
+        <v>69.43572615713052</v>
       </c>
       <c r="H9">
         <v>23.81629408131529</v>
       </c>
       <c r="I9">
-        <v>138.0646013358665</v>
+        <v>134.3828351875439</v>
       </c>
       <c r="J9">
-        <v>92.28136400754896</v>
+        <v>92.90575998301968</v>
       </c>
       <c r="K9">
-        <v>1.51147829263056E-15</v>
+        <v>2.890515813203534E-15</v>
       </c>
       <c r="L9">
-        <v>3304.469166646214</v>
+        <v>3282.128105532771</v>
       </c>
       <c r="M9">
-        <v>2230.641139396661</v>
+        <v>2215.623932984229</v>
       </c>
       <c r="N9">
-        <v>1144.281483512436</v>
+        <v>1143.088010844908</v>
       </c>
       <c r="O9">
-        <v>399.8448725706032</v>
+        <v>396.3803308125862</v>
       </c>
       <c r="P9">
-        <v>139.2252343043226</v>
+        <v>141.3989463342761</v>
       </c>
       <c r="Q9">
         <v>0.769951680159711</v>
       </c>
       <c r="S9">
-        <v>55.62418280156471</v>
+        <v>55.23886723202459</v>
       </c>
       <c r="T9">
-        <v>84.04584480010773</v>
+        <v>84.222061727312</v>
       </c>
       <c r="U9">
-        <v>60.56915600022906</v>
+        <v>60.60463125972671</v>
       </c>
       <c r="V9">
-        <v>389.3947761583281</v>
+        <v>391.4303335162501</v>
       </c>
       <c r="W9">
-        <v>184.9628309474697</v>
+        <v>184.3361450624371</v>
       </c>
       <c r="Z9">
-        <v>-6.34268656961232E-15</v>
+        <v>-6.687372127901107E-15</v>
       </c>
       <c r="AA9">
-        <v>24.07295335440537</v>
+        <v>23.98661980011252</v>
       </c>
       <c r="AB9">
-        <v>45.44752980861593</v>
+        <v>45.449106357018</v>
       </c>
       <c r="AC9">
         <v>-6.278861419867685E-16</v>
@@ -1567,43 +1567,43 @@
         <v>0.7783757766095443</v>
       </c>
       <c r="AH9">
-        <v>1871.305378133717</v>
+        <v>1858.380210295293</v>
       </c>
       <c r="AJ9">
-        <v>493.2086469041249</v>
+        <v>488.2417866996466</v>
       </c>
       <c r="AK9">
-        <v>594.2088750105023</v>
+        <v>591.5661045925568</v>
       </c>
       <c r="AL9">
-        <v>112.5080505617925</v>
+        <v>112.2666393267772</v>
       </c>
       <c r="AM9">
-        <v>150.4654640226338</v>
+        <v>149.4578242064039</v>
       </c>
       <c r="AN9">
-        <v>24.64645468572035</v>
+        <v>24.67924326922379</v>
       </c>
       <c r="AO9">
-        <v>60.720561917257</v>
+        <v>60.08522420370147</v>
       </c>
       <c r="AP9">
-        <v>1661.612062229777</v>
+        <v>1651.037575147466</v>
       </c>
       <c r="AQ9">
-        <v>164.3934601199574</v>
+        <v>164.1243929474149</v>
       </c>
       <c r="AR9">
-        <v>78.51936957770826</v>
+        <v>77.41380278520155</v>
       </c>
       <c r="AS9">
-        <v>42.52857461990821</v>
+        <v>42.17860669083768</v>
       </c>
       <c r="AT9">
-        <v>30.34252179816709</v>
+        <v>30.14143121513374</v>
       </c>
       <c r="AU9">
-        <v>273.2803898727461</v>
+        <v>270.2625288345934</v>
       </c>
       <c r="AV9">
         <v>1</v>
@@ -1616,46 +1616,46 @@
         </is>
       </c>
       <c r="B10">
-        <v>1049.144448435148</v>
+        <v>1039.316769418956</v>
       </c>
       <c r="C10">
-        <v>409.7967542722584</v>
+        <v>412.2567820252812</v>
       </c>
       <c r="D10">
-        <v>8625.410919898761</v>
+        <v>8654.701074828145</v>
       </c>
       <c r="E10">
-        <v>430.9408922170603</v>
+        <v>431.0839610918212</v>
       </c>
       <c r="F10">
-        <v>986.0954855359961</v>
+        <v>976.3806371192888</v>
       </c>
       <c r="G10">
-        <v>59.42296622465666</v>
+        <v>59.30873109488794</v>
       </c>
       <c r="H10">
         <v>55.94800459214945</v>
       </c>
       <c r="I10">
-        <v>448.0284494320294</v>
+        <v>448.1554310418101</v>
       </c>
       <c r="J10">
-        <v>63.75106344565983</v>
+        <v>63.94241783506438</v>
       </c>
       <c r="K10">
         <v>0.003813616686092018</v>
       </c>
       <c r="L10">
-        <v>5046.435505602432</v>
+        <v>5067.397330256596</v>
       </c>
       <c r="M10">
-        <v>2702.475648483372</v>
+        <v>2710.288161201808</v>
       </c>
       <c r="N10">
-        <v>876.4997658129571</v>
+        <v>877.0155833697406</v>
       </c>
       <c r="O10">
-        <v>293.7427468363926</v>
+        <v>293.8899699968011</v>
       </c>
       <c r="P10">
         <v>128.297009046822</v>
@@ -1667,28 +1667,28 @@
         <v>203.0695822454308</v>
       </c>
       <c r="S10">
-        <v>90.08850434898284</v>
+        <v>90.08435006333522</v>
       </c>
       <c r="T10">
-        <v>102.5978702832541</v>
+        <v>102.4013759066123</v>
       </c>
       <c r="U10">
-        <v>221.208280669138</v>
+        <v>221.1378608176974</v>
       </c>
       <c r="V10">
-        <v>427.7800852626311</v>
+        <v>418.2076498712406</v>
       </c>
       <c r="W10">
-        <v>239.6151266635368</v>
+        <v>239.7367905269326</v>
       </c>
       <c r="Z10">
         <v>1.755153244749021</v>
       </c>
       <c r="AA10">
-        <v>36.36790491329101</v>
+        <v>36.43590601576207</v>
       </c>
       <c r="AB10">
-        <v>34.2797098299915</v>
+        <v>34.24340078832319</v>
       </c>
       <c r="AC10">
         <v>-2.019169747409806E-15</v>
@@ -1706,43 +1706,43 @@
         <v>53.78938066054137</v>
       </c>
       <c r="AH10">
-        <v>3639.300559762842</v>
+        <v>3656.126721463409</v>
       </c>
       <c r="AJ10">
-        <v>220.3444655827873</v>
+        <v>216.4944029230494</v>
       </c>
       <c r="AK10">
-        <v>616.1131164216083</v>
+        <v>618.9551063176997</v>
       </c>
       <c r="AL10">
-        <v>99.16416880845948</v>
+        <v>99.2284070780986</v>
       </c>
       <c r="AM10">
-        <v>50.06964533972609</v>
+        <v>50.32326897428481</v>
       </c>
       <c r="AN10">
-        <v>49.65948560744007</v>
+        <v>49.83752518008421</v>
       </c>
       <c r="AO10">
-        <v>384.7022085587836</v>
+        <v>389.6178295036551</v>
       </c>
       <c r="AP10">
-        <v>2161.514190638619</v>
+        <v>2169.559165869844</v>
       </c>
       <c r="AQ10">
-        <v>173.986197156752</v>
+        <v>173.9947059497375</v>
       </c>
       <c r="AR10">
-        <v>81.93170741334393</v>
+        <v>81.9128302134512</v>
       </c>
       <c r="AS10">
-        <v>39.8645691473441</v>
+        <v>39.958757403516</v>
       </c>
       <c r="AT10">
         <v>58.36187574216106</v>
       </c>
       <c r="AU10">
-        <v>263.8686388997654</v>
+        <v>263.747461852849</v>
       </c>
       <c r="AV10">
         <v>1</v>
@@ -1755,22 +1755,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>318.7325877107284</v>
+        <v>318.521259280443</v>
       </c>
       <c r="C11">
         <v>99.58018862601645</v>
       </c>
       <c r="D11">
-        <v>6650.914866291366</v>
+        <v>6656.238925978912</v>
       </c>
       <c r="E11">
-        <v>134.4373418070505</v>
+        <v>134.3174283895547</v>
       </c>
       <c r="F11">
-        <v>293.0574037686495</v>
+        <v>292.9492474609598</v>
       </c>
       <c r="G11">
-        <v>23.29100169029511</v>
+        <v>23.18842537787995</v>
       </c>
       <c r="H11">
         <v>27.57386099503913</v>
@@ -1785,16 +1785,16 @@
         <v>0.1074401983122751</v>
       </c>
       <c r="L11">
-        <v>4769.201654290126</v>
+        <v>4774.865973346742</v>
       </c>
       <c r="M11">
-        <v>769.4104096926828</v>
+        <v>769.6370562008617</v>
       </c>
       <c r="N11">
-        <v>1112.302802308557</v>
+        <v>1111.735896431308</v>
       </c>
       <c r="O11">
-        <v>99.50527337437251</v>
+        <v>99.52315481542912</v>
       </c>
       <c r="P11">
         <v>43.24644508654328</v>
@@ -1803,28 +1803,28 @@
         <v>0.05101405951883867</v>
       </c>
       <c r="S11">
-        <v>20.40888915948232</v>
+        <v>20.33863131696107</v>
       </c>
       <c r="T11">
-        <v>7.05489594799883</v>
+        <v>7.02372136277474</v>
       </c>
       <c r="U11">
-        <v>16.61549882393017</v>
+        <v>16.59552090792729</v>
       </c>
       <c r="V11">
-        <v>122.7824398062903</v>
+        <v>122.9148989312726</v>
       </c>
       <c r="W11">
-        <v>147.1115992188831</v>
+        <v>146.9166435377674</v>
       </c>
       <c r="Z11">
-        <v>2.436851119263937</v>
+        <v>2.419568487212419</v>
       </c>
       <c r="AA11">
         <v>21.53980798000725</v>
       </c>
       <c r="AB11">
-        <v>10.08551793444234</v>
+        <v>10.03401659930062</v>
       </c>
       <c r="AC11">
         <v>7.683167832258924E-16</v>
@@ -1842,31 +1842,31 @@
         <v>8.791194982583958</v>
       </c>
       <c r="AH11">
-        <v>1914.565532397556</v>
+        <v>1916.907239000792</v>
       </c>
       <c r="AJ11">
-        <v>103.2032133339407</v>
+        <v>109.3722873166898</v>
       </c>
       <c r="AK11">
-        <v>830.6492503791078</v>
+        <v>829.1673939653311</v>
       </c>
       <c r="AL11">
-        <v>194.1622217705772</v>
+        <v>194.0001089097339</v>
       </c>
       <c r="AM11">
-        <v>1535.795672173236</v>
+        <v>1534.147161617151</v>
       </c>
       <c r="AN11">
-        <v>38.40382053523192</v>
+        <v>38.46809458243966</v>
       </c>
       <c r="AO11">
-        <v>152.4219437004756</v>
+        <v>152.8036879546037</v>
       </c>
       <c r="AP11">
-        <v>666.5532137744224</v>
+        <v>666.930664982128</v>
       </c>
       <c r="AQ11">
-        <v>39.95995900843643</v>
+        <v>40.06409561799442</v>
       </c>
       <c r="AR11">
         <v>44.54157107925538</v>
@@ -1878,7 +1878,7 @@
         <v>1.623434422464218</v>
       </c>
       <c r="AU11">
-        <v>42.59205918893312</v>
+        <v>42.43297512723149</v>
       </c>
       <c r="AV11">
         <v>1</v>
@@ -1891,49 +1891,49 @@
         </is>
       </c>
       <c r="B12">
-        <v>635.9576423575299</v>
+        <v>636.1019734491194</v>
       </c>
       <c r="C12">
-        <v>134.2013268511154</v>
+        <v>134.2236744739835</v>
       </c>
       <c r="D12">
-        <v>7421.00688504257</v>
+        <v>7419.737656659454</v>
       </c>
       <c r="E12">
-        <v>419.9405341995698</v>
+        <v>419.9879965064214</v>
       </c>
       <c r="F12">
-        <v>587.7017515407733</v>
+        <v>587.700718927465</v>
       </c>
       <c r="G12">
-        <v>48.57452415415532</v>
+        <v>48.66407122056039</v>
       </c>
       <c r="H12">
         <v>5.906751538980122</v>
       </c>
       <c r="I12">
-        <v>184.1910589354859</v>
+        <v>184.2848237783499</v>
       </c>
       <c r="J12">
-        <v>84.73251659398673</v>
+        <v>84.72948737748592</v>
       </c>
       <c r="K12">
         <v>1.202312530062143</v>
       </c>
       <c r="L12">
-        <v>4691.867807084325</v>
+        <v>4689.044019453602</v>
       </c>
       <c r="M12">
-        <v>1880.311934955559</v>
+        <v>1879.836437679636</v>
       </c>
       <c r="N12">
-        <v>851.0366752411767</v>
+        <v>850.8571995262148</v>
       </c>
       <c r="O12">
-        <v>297.8787973958964</v>
+        <v>297.9625267500586</v>
       </c>
       <c r="P12">
-        <v>108.0163551956808</v>
+        <v>108.2254113642338</v>
       </c>
       <c r="Q12">
         <v>2.143594943452089</v>
@@ -1942,28 +1942,28 @@
         <v>9.187907008118041</v>
       </c>
       <c r="S12">
-        <v>59.29358193895882</v>
+        <v>59.26362485220776</v>
       </c>
       <c r="T12">
-        <v>76.44506982475801</v>
+        <v>77.32442363994856</v>
       </c>
       <c r="U12">
-        <v>73.36738311409319</v>
+        <v>73.42560402527188</v>
       </c>
       <c r="V12">
-        <v>264.9974848137865</v>
+        <v>265.1431482737749</v>
       </c>
       <c r="W12">
-        <v>171.2375580277482</v>
+        <v>171.355940836935</v>
       </c>
       <c r="Z12">
-        <v>5.270332338473252</v>
+        <v>2.98419387534322</v>
       </c>
       <c r="AA12">
-        <v>20.88901255489865</v>
+        <v>20.89614167912072</v>
       </c>
       <c r="AB12">
-        <v>30.65609844531507</v>
+        <v>30.72723577724046</v>
       </c>
       <c r="AC12">
         <v>2.521289410518147E-17</v>
@@ -1981,43 +1981,43 @@
         <v>4.253247242372497</v>
       </c>
       <c r="AH12">
-        <v>3524.386772306313</v>
+        <v>3522.294153741738</v>
       </c>
       <c r="AJ12">
-        <v>254.0507675740037</v>
+        <v>253.8480592821876</v>
       </c>
       <c r="AK12">
-        <v>680.0702423364277</v>
+        <v>680.0712408508746</v>
       </c>
       <c r="AL12">
-        <v>81.93064380452589</v>
+        <v>81.90445319514635</v>
       </c>
       <c r="AM12">
-        <v>56.92835263920217</v>
+        <v>56.76151330054406</v>
       </c>
       <c r="AN12">
-        <v>36.16172790141364</v>
+        <v>36.09854410962389</v>
       </c>
       <c r="AO12">
-        <v>70.00518168784201</v>
+        <v>68.39837831933046</v>
       </c>
       <c r="AP12">
-        <v>1246.600262214744</v>
+        <v>1246.126706878465</v>
       </c>
       <c r="AQ12">
-        <v>195.739410788379</v>
+        <v>196.0154155260236</v>
       </c>
       <c r="AR12">
-        <v>267.3865082406565</v>
+        <v>267.3801775608055</v>
       </c>
       <c r="AS12">
-        <v>14.0125771381866</v>
+        <v>14.00519215672366</v>
       </c>
       <c r="AT12">
         <v>76.7955829353841</v>
       </c>
       <c r="AU12">
-        <v>149.4889290294792</v>
+        <v>149.2322731849108</v>
       </c>
       <c r="AV12">
         <v>1</v>
@@ -2084,19 +2084,19 @@
         <v>88.16812547500497</v>
       </c>
       <c r="T13">
-        <v>182.9200999503024</v>
+        <v>182.307777661898</v>
       </c>
       <c r="U13">
-        <v>342.4422335398873</v>
+        <v>342.4399174390605</v>
       </c>
       <c r="V13">
-        <v>545.4720827939356</v>
+        <v>545.4486344958082</v>
       </c>
       <c r="W13">
-        <v>369.4784555833429</v>
+        <v>370.1162161390691</v>
       </c>
       <c r="Z13">
-        <v>13.55570587872654</v>
+        <v>13.55570587872655</v>
       </c>
       <c r="AA13">
         <v>37.73029824460362</v>
@@ -2166,82 +2166,82 @@
         </is>
       </c>
       <c r="B14">
-        <v>1394.395683364409</v>
+        <v>1392.226961263706</v>
       </c>
       <c r="C14">
-        <v>298.3830888369537</v>
+        <v>297.3678536143105</v>
       </c>
       <c r="D14">
-        <v>9803.339120914075</v>
+        <v>9814.206060062555</v>
       </c>
       <c r="E14">
-        <v>540.5631098915642</v>
+        <v>538.8449909884678</v>
       </c>
       <c r="F14">
-        <v>1308.366447289934</v>
+        <v>1306.591571455213</v>
       </c>
       <c r="G14">
-        <v>79.9435492507365</v>
+        <v>79.54759545858333</v>
       </c>
       <c r="H14">
-        <v>21.60945136379287</v>
+        <v>21.89674323205076</v>
       </c>
       <c r="I14">
-        <v>267.7352360745447</v>
+        <v>266.2163498098935</v>
       </c>
       <c r="J14">
-        <v>94.62030381818064</v>
+        <v>94.5023270673733</v>
       </c>
       <c r="K14">
-        <v>8.253887993201079</v>
+        <v>8.036680414432629</v>
       </c>
       <c r="L14">
-        <v>3995.155849193381</v>
+        <v>4004.197898627362</v>
       </c>
       <c r="M14">
-        <v>4511.68493271653</v>
+        <v>4513.953304083222</v>
       </c>
       <c r="N14">
-        <v>1296.498339004165</v>
+        <v>1296.054857351973</v>
       </c>
       <c r="O14">
-        <v>339.0797619044193</v>
+        <v>339.2673753569248</v>
       </c>
       <c r="P14">
-        <v>122.9334257907968</v>
+        <v>120.7538243486655</v>
       </c>
       <c r="Q14">
         <v>1.085587067997094</v>
       </c>
       <c r="S14">
-        <v>103.8357983797181</v>
+        <v>103.3009675188097</v>
       </c>
       <c r="T14">
-        <v>165.1275984536931</v>
+        <v>163.9023286281575</v>
       </c>
       <c r="U14">
-        <v>311.0444595090846</v>
+        <v>311.3972113845477</v>
       </c>
       <c r="V14">
-        <v>477.8768701586687</v>
+        <v>479.224546748916</v>
       </c>
       <c r="W14">
-        <v>351.6153416875062</v>
+        <v>349.3892678443963</v>
       </c>
       <c r="Z14">
-        <v>8.54911689686357</v>
+        <v>8.477275578402528</v>
       </c>
       <c r="AA14">
-        <v>44.78986584591878</v>
+        <v>44.2425351455295</v>
       </c>
       <c r="AB14">
-        <v>36.56898569081153</v>
+        <v>36.69951727845041</v>
       </c>
       <c r="AC14">
-        <v>-5.140588069350847E-17</v>
+        <v>1.116450802501368E-16</v>
       </c>
       <c r="AD14">
-        <v>15.71861767645358</v>
+        <v>16.13469555462018</v>
       </c>
       <c r="AE14">
         <v>7.192318955928982</v>
@@ -2253,43 +2253,43 @@
         <v>0.2823638017250977</v>
       </c>
       <c r="AH14">
-        <v>2581.981615623111</v>
+        <v>2592.530395781424</v>
       </c>
       <c r="AJ14">
-        <v>145.5289301513234</v>
+        <v>144.9499524610576</v>
       </c>
       <c r="AK14">
-        <v>608.0545677318486</v>
+        <v>610.628327095541</v>
       </c>
       <c r="AL14">
-        <v>111.1414208628443</v>
+        <v>111.1185824621287</v>
       </c>
       <c r="AM14">
-        <v>60.28820769942612</v>
+        <v>60.08291450989151</v>
       </c>
       <c r="AN14">
-        <v>30.9574943881864</v>
+        <v>31.14671038059559</v>
       </c>
       <c r="AO14">
-        <v>464.5239716894279</v>
+        <v>460.932851752222</v>
       </c>
       <c r="AP14">
-        <v>3421.143945227376</v>
+        <v>3420.135016666493</v>
       </c>
       <c r="AQ14">
-        <v>211.0647547527794</v>
+        <v>210.5737899619185</v>
       </c>
       <c r="AR14">
-        <v>313.1197214053221</v>
+        <v>318.3983314428193</v>
       </c>
       <c r="AS14">
-        <v>11.4393156894799</v>
+        <v>11.5142820034529</v>
       </c>
       <c r="AT14">
-        <v>86.15095166396365</v>
+        <v>86.87674977613645</v>
       </c>
       <c r="AU14">
-        <v>520.5226103350665</v>
+        <v>518.6991563548953</v>
       </c>
       <c r="AV14">
         <v>1</v>
@@ -2302,76 +2302,76 @@
         </is>
       </c>
       <c r="B15">
-        <v>475.1053670414807</v>
+        <v>473.3028653390864</v>
       </c>
       <c r="C15">
-        <v>107.6486137744406</v>
+        <v>108.258172938994</v>
       </c>
       <c r="D15">
-        <v>6013.394005850463</v>
+        <v>6035.233105755449</v>
       </c>
       <c r="E15">
-        <v>140.0080824030472</v>
+        <v>138.3380154391594</v>
       </c>
       <c r="F15">
-        <v>436.3991994009299</v>
+        <v>435.4137291455066</v>
       </c>
       <c r="G15">
-        <v>33.50032345256311</v>
+        <v>32.88198834864507</v>
       </c>
       <c r="H15">
         <v>26.23745470745819</v>
       </c>
       <c r="I15">
-        <v>197.8987299971272</v>
+        <v>200.5276748368377</v>
       </c>
       <c r="J15">
-        <v>62.51381570492039</v>
+        <v>62.76029713567787</v>
       </c>
       <c r="K15">
-        <v>-7.08522302618731E-15</v>
+        <v>-7.120893416328675E-15</v>
       </c>
       <c r="L15">
-        <v>3883.476791521656</v>
+        <v>3897.811331621961</v>
       </c>
       <c r="M15">
-        <v>1089.028781592539</v>
+        <v>1088.785959622104</v>
       </c>
       <c r="N15">
-        <v>1040.888432736268</v>
+        <v>1048.635814511385</v>
       </c>
       <c r="O15">
-        <v>106.8244741268239</v>
+        <v>105.8110603281676</v>
       </c>
       <c r="P15">
-        <v>19.69092980349814</v>
+        <v>19.84973955381462</v>
       </c>
       <c r="S15">
-        <v>23.65069781579957</v>
+        <v>22.82937242821209</v>
       </c>
       <c r="T15">
-        <v>21.59153431203467</v>
+        <v>21.37363859645382</v>
       </c>
       <c r="U15">
-        <v>23.6502280061936</v>
+        <v>23.29328512963192</v>
       </c>
       <c r="V15">
-        <v>193.4033695304267</v>
+        <v>191.9667792202998</v>
       </c>
       <c r="W15">
-        <v>200.9788523917395</v>
+        <v>202.1810809460475</v>
       </c>
       <c r="Z15">
-        <v>0.06291593012461295</v>
+        <v>0.06136245036844901</v>
       </c>
       <c r="AA15">
-        <v>23.53587743080461</v>
+        <v>23.1961043169057</v>
       </c>
       <c r="AB15">
-        <v>12.98533712937002</v>
+        <v>12.62919441888897</v>
       </c>
       <c r="AC15">
-        <v>7.307972697119744E-16</v>
+        <v>7.287403217525325E-16</v>
       </c>
       <c r="AD15">
         <v>1.03155306216269</v>
@@ -2386,43 +2386,43 @@
         <v>5.013613556515284</v>
       </c>
       <c r="AH15">
-        <v>1414.311031845099</v>
+        <v>1406.4733558701</v>
       </c>
       <c r="AJ15">
-        <v>221.7006899327004</v>
+        <v>231.4439710940003</v>
       </c>
       <c r="AK15">
-        <v>720.7921937163848</v>
+        <v>715.5845318049729</v>
       </c>
       <c r="AL15">
-        <v>190.4414575044852</v>
+        <v>191.6580259577526</v>
       </c>
       <c r="AM15">
-        <v>1165.398330848308</v>
+        <v>1180.372259089934</v>
       </c>
       <c r="AN15">
-        <v>27.64933578343542</v>
+        <v>27.53041427309426</v>
       </c>
       <c r="AO15">
-        <v>152.6523841660987</v>
+        <v>153.9694046264806</v>
       </c>
       <c r="AP15">
-        <v>881.0289379879179</v>
+        <v>881.0601160675498</v>
       </c>
       <c r="AQ15">
-        <v>48.63499276498514</v>
+        <v>48.72836396249765</v>
       </c>
       <c r="AR15">
-        <v>32.38439920628989</v>
+        <v>32.22465026579661</v>
       </c>
       <c r="AS15">
-        <v>7.706429755282281</v>
+        <v>7.572948010799597</v>
       </c>
       <c r="AT15">
         <v>101.4534088611079</v>
       </c>
       <c r="AU15">
-        <v>116.8005401918979</v>
+        <v>117.3128144332659</v>
       </c>
       <c r="AV15">
         <v>1</v>
@@ -2435,46 +2435,46 @@
         </is>
       </c>
       <c r="B16">
-        <v>379.4155540238518</v>
+        <v>379.7486089622447</v>
       </c>
       <c r="C16">
-        <v>134.1544056181487</v>
+        <v>140.6526720018235</v>
       </c>
       <c r="D16">
-        <v>7748.627321036065</v>
+        <v>7784.377912004225</v>
       </c>
       <c r="E16">
-        <v>245.9490811746833</v>
+        <v>247.9120219212125</v>
       </c>
       <c r="F16">
-        <v>367.5497615346996</v>
+        <v>367.9377995511138</v>
       </c>
       <c r="G16">
-        <v>10.89874544438861</v>
+        <v>10.84473420849774</v>
       </c>
       <c r="H16">
         <v>45.18307473629735</v>
       </c>
       <c r="I16">
-        <v>207.1331987580212</v>
+        <v>223.2863218676609</v>
       </c>
       <c r="J16">
-        <v>46.66963840732476</v>
+        <v>46.54317744109431</v>
       </c>
       <c r="K16">
         <v>3.853790141072231</v>
       </c>
       <c r="L16">
-        <v>5655.750772645161</v>
+        <v>5675.976002873819</v>
       </c>
       <c r="M16">
-        <v>793.243764352591</v>
+        <v>805.048985690783</v>
       </c>
       <c r="N16">
-        <v>1299.632784038313</v>
+        <v>1303.352923439622</v>
       </c>
       <c r="O16">
-        <v>201.890044899241</v>
+        <v>203.7777217227271</v>
       </c>
       <c r="P16">
         <v>20.00849071406119</v>
@@ -2483,28 +2483,28 @@
         <v>33.71763317599461</v>
       </c>
       <c r="S16">
-        <v>40.10502816223625</v>
+        <v>40.19851332082404</v>
       </c>
       <c r="T16">
-        <v>17.61476387404759</v>
+        <v>17.63340161246707</v>
       </c>
       <c r="U16">
-        <v>14.57025360273143</v>
+        <v>14.45166123875386</v>
       </c>
       <c r="V16">
-        <v>140.1103401983291</v>
+        <v>139.8440399659864</v>
       </c>
       <c r="W16">
-        <v>196.9300969859272</v>
+        <v>197.7314997649434</v>
       </c>
       <c r="Z16">
-        <v>0.09454674044410333</v>
+        <v>0.0937717671617742</v>
       </c>
       <c r="AA16">
-        <v>7.066658456748383</v>
+        <v>7.017095929710732</v>
       </c>
       <c r="AB16">
-        <v>6.896860997656432</v>
+        <v>6.81050654127645</v>
       </c>
       <c r="AC16">
         <v>6.449656078781993E-17</v>
@@ -2516,43 +2516,43 @@
         <v>2.437539222821127</v>
       </c>
       <c r="AH16">
-        <v>3675.21750031994</v>
+        <v>3695.23122032374</v>
       </c>
       <c r="AJ16">
-        <v>82.61082638839591</v>
+        <v>82.87740025317493</v>
       </c>
       <c r="AK16">
-        <v>995.898068655364</v>
+        <v>995.6362520871581</v>
       </c>
       <c r="AL16">
-        <v>156.0597382561055</v>
+        <v>156.3554714512377</v>
       </c>
       <c r="AM16">
-        <v>573.606545293015</v>
+        <v>573.5745906321757</v>
       </c>
       <c r="AN16">
-        <v>67.7709779867744</v>
+        <v>67.61061304489429</v>
       </c>
       <c r="AO16">
-        <v>105.6657853324349</v>
+        <v>105.7658717337487</v>
       </c>
       <c r="AP16">
-        <v>676.2041743139666</v>
+        <v>687.8417579205335</v>
       </c>
       <c r="AQ16">
-        <v>38.3443248121819</v>
+        <v>38.26118191788368</v>
       </c>
       <c r="AR16">
-        <v>18.21096932871417</v>
+        <v>18.26430478079749</v>
       </c>
       <c r="AS16">
-        <v>7.488004740079988</v>
+        <v>7.54137914385418</v>
       </c>
       <c r="AT16">
         <v>45.62358850734597</v>
       </c>
       <c r="AU16">
-        <v>57.05262736568975</v>
+        <v>57.20406632301592</v>
       </c>
       <c r="AV16">
         <v>1</v>
@@ -2695,73 +2695,73 @@
         </is>
       </c>
       <c r="B18">
-        <v>429.6453507468882</v>
+        <v>428.9360747157584</v>
       </c>
       <c r="C18">
-        <v>126.3156274146282</v>
+        <v>125.5901701475724</v>
       </c>
       <c r="D18">
-        <v>7893.320919945343</v>
+        <v>7900.908570100449</v>
       </c>
       <c r="E18">
-        <v>210.1402185134369</v>
+        <v>210.9167592413834</v>
       </c>
       <c r="F18">
-        <v>418.4641140278596</v>
+        <v>417.7849539155561</v>
       </c>
       <c r="G18">
-        <v>10.65996334144459</v>
+        <v>10.75233069495926</v>
       </c>
       <c r="H18">
         <v>45.26523181662782</v>
       </c>
       <c r="I18">
-        <v>189.9203097340886</v>
+        <v>191.0183080356065</v>
       </c>
       <c r="J18">
-        <v>65.07225695793278</v>
+        <v>64.51600954687473</v>
       </c>
       <c r="K18">
         <v>0.07087164463178135</v>
       </c>
       <c r="L18">
-        <v>5742.425055580377</v>
+        <v>5743.714550276962</v>
       </c>
       <c r="M18">
-        <v>902.7702746776617</v>
+        <v>910.6865221124923</v>
       </c>
       <c r="N18">
-        <v>1248.125589687304</v>
+        <v>1246.507497710995</v>
       </c>
       <c r="O18">
-        <v>169.8343890796851</v>
+        <v>170.852885870101</v>
       </c>
       <c r="P18">
-        <v>26.23621485282043</v>
+        <v>28.33009556831703</v>
       </c>
       <c r="S18">
-        <v>35.39402665308685</v>
+        <v>34.75198045222304</v>
       </c>
       <c r="T18">
-        <v>8.957394090389529</v>
+        <v>8.824067396595133</v>
       </c>
       <c r="U18">
-        <v>13.63845131019322</v>
+        <v>13.58591608249533</v>
       </c>
       <c r="V18">
-        <v>200.1680049784581</v>
+        <v>201.9675143617488</v>
       </c>
       <c r="W18">
-        <v>196.3917901350173</v>
+        <v>194.1684450649516</v>
       </c>
       <c r="Z18">
-        <v>0.7742104280145806</v>
+        <v>0.7697759007229066</v>
       </c>
       <c r="AA18">
-        <v>7.137028385718112</v>
+        <v>7.060260112064665</v>
       </c>
       <c r="AB18">
-        <v>6.209808027191561</v>
+        <v>6.459946896146879</v>
       </c>
       <c r="AC18">
         <v>1.987432063814836E-16</v>
@@ -2776,43 +2776,43 @@
         <v>12.84229579139863</v>
       </c>
       <c r="AH18">
-        <v>3102.636923803904</v>
+        <v>3108.902964716199</v>
       </c>
       <c r="AJ18">
-        <v>58.34804118255609</v>
+        <v>58.31691938637424</v>
       </c>
       <c r="AK18">
-        <v>1055.280661545781</v>
+        <v>1055.976935304631</v>
       </c>
       <c r="AL18">
-        <v>187.8554097099199</v>
+        <v>187.31255113113</v>
       </c>
       <c r="AM18">
-        <v>1114.4423415445</v>
+        <v>1108.202636133514</v>
       </c>
       <c r="AN18">
-        <v>119.9686562983284</v>
+        <v>122.0806407828181</v>
       </c>
       <c r="AO18">
-        <v>104.7072529907342</v>
+        <v>103.7272490730512</v>
       </c>
       <c r="AP18">
-        <v>794.186663787202</v>
+        <v>801.9069587060185</v>
       </c>
       <c r="AQ18">
-        <v>39.75720581043812</v>
+        <v>39.77541708687345</v>
       </c>
       <c r="AR18">
-        <v>28.64960850468716</v>
+        <v>28.47045315206075</v>
       </c>
       <c r="AS18">
-        <v>6.990108591644944</v>
+        <v>6.908292160906424</v>
       </c>
       <c r="AT18">
         <v>0.492566705111465</v>
       </c>
       <c r="AU18">
-        <v>42.56256873981617</v>
+        <v>43.01416446960202</v>
       </c>
       <c r="AV18">
         <v>1</v>
@@ -2825,130 +2825,133 @@
         </is>
       </c>
       <c r="B19">
-        <v>976.0242920157862</v>
+        <v>964.054029083438</v>
       </c>
       <c r="C19">
-        <v>270.9515228021964</v>
+        <v>264.2437699172431</v>
       </c>
       <c r="D19">
-        <v>7492.955644707528</v>
+        <v>7531.667162058182</v>
       </c>
       <c r="E19">
-        <v>871.203589034183</v>
+        <v>877.6361149235962</v>
       </c>
       <c r="F19">
-        <v>873.8255846853172</v>
+        <v>870.0887962253997</v>
       </c>
       <c r="G19">
-        <v>94.24320197952296</v>
+        <v>92.22570790681783</v>
       </c>
       <c r="H19">
-        <v>25.66515204522582</v>
+        <v>5.631343486154424</v>
       </c>
       <c r="I19">
-        <v>375.8625181183115</v>
+        <v>364.9812246283638</v>
       </c>
       <c r="J19">
-        <v>100.9148117134511</v>
+        <v>101.3903264772311</v>
       </c>
       <c r="K19">
-        <v>8.94761162926909</v>
+        <v>4.29366546137942</v>
       </c>
       <c r="L19">
-        <v>4329.897670921562</v>
+        <v>4370.650923156331</v>
       </c>
       <c r="M19">
-        <v>2262.235294188189</v>
+        <v>2264.358395915931</v>
       </c>
       <c r="N19">
-        <v>900.8226795977768</v>
+        <v>896.657842985919</v>
       </c>
       <c r="O19">
-        <v>627.434018940983</v>
+        <v>623.5097857502074</v>
       </c>
       <c r="P19">
-        <v>138.1313082622489</v>
+        <v>150.2838500614095</v>
       </c>
       <c r="Q19">
-        <v>6.921312955641977</v>
+        <v>6.750146343515633</v>
       </c>
       <c r="R19">
         <v>1.041897762916584</v>
       </c>
       <c r="S19">
-        <v>130.7859342410308</v>
+        <v>131.5036161528378</v>
       </c>
       <c r="T19">
-        <v>179.9506410743442</v>
+        <v>179.0603276904858</v>
       </c>
       <c r="U19">
-        <v>129.0029670936583</v>
+        <v>128.992615684043</v>
       </c>
       <c r="V19">
-        <v>277.1246801823983</v>
+        <v>274.7602779552885</v>
       </c>
       <c r="W19">
-        <v>286.7111406459457</v>
+        <v>286.2692290526041</v>
       </c>
       <c r="Z19">
-        <v>1.937421613968987</v>
+        <v>1.887561498903609</v>
       </c>
       <c r="AA19">
-        <v>30.55513512454185</v>
+        <v>28.73987136289675</v>
       </c>
       <c r="AB19">
-        <v>65.16466540816378</v>
+        <v>64.90082446364411</v>
       </c>
       <c r="AC19">
-        <v>-1.067613514468407E-15</v>
+        <v>4.440056909738209E-17</v>
       </c>
       <c r="AD19">
-        <v>15.97727585174803</v>
+        <v>2.719436677613476</v>
+      </c>
+      <c r="AE19">
+        <v>9.70717674858223</v>
       </c>
       <c r="AF19">
         <v>13.47877030885351</v>
       </c>
       <c r="AG19">
-        <v>79.86686066667296</v>
+        <v>17.42802273315979</v>
       </c>
       <c r="AH19">
-        <v>3388.334067822414</v>
+        <v>3420.217523764472</v>
       </c>
       <c r="AJ19">
-        <v>100.7332056316056</v>
+        <v>103.910460294863</v>
       </c>
       <c r="AK19">
-        <v>435.6238176047293</v>
+        <v>434.7925094731169</v>
       </c>
       <c r="AL19">
-        <v>89.978431798671</v>
+        <v>90.82463506167618</v>
       </c>
       <c r="AM19">
-        <v>50.6593289244055</v>
+        <v>50.27267257888161</v>
       </c>
       <c r="AN19">
-        <v>34.15301745536157</v>
+        <v>34.19976279339867</v>
       </c>
       <c r="AO19">
-        <v>244.2911116575349</v>
+        <v>250.3285429778689</v>
       </c>
       <c r="AP19">
-        <v>1742.188091148902</v>
+        <v>1741.235515024803</v>
       </c>
       <c r="AQ19">
-        <v>226.7861354171087</v>
+        <v>225.5612832083159</v>
       </c>
       <c r="AR19">
-        <v>81.84302045990877</v>
+        <v>81.78504013388185</v>
       </c>
       <c r="AS19">
-        <v>60.42742990914245</v>
+        <v>60.2847516180231</v>
       </c>
       <c r="AT19">
-        <v>9.45701318928346</v>
+        <v>9.237490706711132</v>
       </c>
       <c r="AU19">
-        <v>167.7903642739971</v>
+        <v>172.3146822861723</v>
       </c>
       <c r="AV19">
         <v>1</v>
@@ -2961,28 +2964,28 @@
         </is>
       </c>
       <c r="B20">
-        <v>1302.528744808133</v>
+        <v>1315.705347105869</v>
       </c>
       <c r="C20">
-        <v>312.7202948024716</v>
+        <v>315.9147072211165</v>
       </c>
       <c r="D20">
-        <v>8542.324509769967</v>
+        <v>8546.03893076788</v>
       </c>
       <c r="E20">
-        <v>691.3150512194718</v>
+        <v>723.2332504640841</v>
       </c>
       <c r="F20">
-        <v>1218.16613498261</v>
+        <v>1230.890121205044</v>
       </c>
       <c r="G20">
-        <v>84.77310319762761</v>
+        <v>85.23110755953932</v>
       </c>
       <c r="H20">
         <v>16.62705552292083</v>
       </c>
       <c r="I20">
-        <v>264.8440938233483</v>
+        <v>264.89185477325</v>
       </c>
       <c r="J20">
         <v>87.58133598729383</v>
@@ -2991,19 +2994,19 @@
         <v>0.3407633428009137</v>
       </c>
       <c r="L20">
-        <v>5030.387783290327</v>
+        <v>5033.315515691625</v>
       </c>
       <c r="M20">
-        <v>2600.558162834371</v>
+        <v>2601.344851430987</v>
       </c>
       <c r="N20">
         <v>911.3785636452682</v>
       </c>
       <c r="O20">
-        <v>543.6396347054947</v>
+        <v>564.3915418577335</v>
       </c>
       <c r="P20">
-        <v>55.10586420646979</v>
+        <v>58.93441972944218</v>
       </c>
       <c r="Q20">
         <v>1.869257194710915</v>
@@ -3012,25 +3015,25 @@
         <v>0.4500406805860108</v>
       </c>
       <c r="S20">
-        <v>116.5295249870848</v>
+        <v>125.533809254721</v>
       </c>
       <c r="T20">
         <v>260.8298481635896</v>
       </c>
       <c r="U20">
-        <v>63.48807385412292</v>
+        <v>63.48824324996715</v>
       </c>
       <c r="V20">
-        <v>555.5508202274164</v>
+        <v>554.2037583135981</v>
       </c>
       <c r="W20">
-        <v>347.7003708979224</v>
+        <v>351.1447650368566</v>
       </c>
       <c r="Z20">
-        <v>1.650762658536451</v>
+        <v>1.624969491996817</v>
       </c>
       <c r="AA20">
-        <v>33.48138535230559</v>
+        <v>33.95056055231272</v>
       </c>
       <c r="AB20">
         <v>52.08889368704357</v>
@@ -3045,28 +3048,28 @@
         <v>9.326571642910727</v>
       </c>
       <c r="AH20">
-        <v>1273.463378525792</v>
+        <v>1273.367638524937</v>
       </c>
       <c r="AJ20">
-        <v>2640.199872326787</v>
+        <v>2640.169467348677</v>
       </c>
       <c r="AK20">
-        <v>852.9933709798016</v>
+        <v>846.0450091807576</v>
       </c>
       <c r="AL20">
-        <v>95.05639977349179</v>
+        <v>95.05572579226686</v>
       </c>
       <c r="AM20">
-        <v>36.9666722080155</v>
+        <v>36.93277410008073</v>
       </c>
       <c r="AN20">
         <v>17.35898704408823</v>
       </c>
       <c r="AO20">
-        <v>126.7365967963998</v>
+        <v>126.7365967306127</v>
       </c>
       <c r="AP20">
-        <v>1855.915637757537</v>
+        <v>1855.91555032649</v>
       </c>
       <c r="AQ20">
         <v>137.5848558477437</v>
@@ -3075,13 +3078,13 @@
         <v>149.4243403137135</v>
       </c>
       <c r="AS20">
-        <v>19.27028285513146</v>
+        <v>19.1796298637569</v>
       </c>
       <c r="AT20">
         <v>346.5683223979797</v>
       </c>
       <c r="AU20">
-        <v>125.017250061003</v>
+        <v>125.6477062601427</v>
       </c>
       <c r="AV20">
         <v>1</v>
@@ -3224,22 +3227,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>735.3055150006805</v>
+        <v>737.7889157029288</v>
       </c>
       <c r="C22">
-        <v>170.0816171519465</v>
+        <v>173.5014005714714</v>
       </c>
       <c r="D22">
-        <v>7074.101274406649</v>
+        <v>7028.590764592286</v>
       </c>
       <c r="E22">
-        <v>702.3866317830813</v>
+        <v>700.0411546514875</v>
       </c>
       <c r="F22">
-        <v>636.1082541038918</v>
+        <v>637.6769757419282</v>
       </c>
       <c r="G22">
-        <v>97.24737017016193</v>
+        <v>98.12381608287126</v>
       </c>
       <c r="H22">
         <v>20.27886355691953</v>
@@ -3248,52 +3251,52 @@
         <v>199.3410962151297</v>
       </c>
       <c r="J22">
-        <v>54.9112007990169</v>
+        <v>56.0260725267572</v>
       </c>
       <c r="K22">
         <v>3.643809541906234</v>
       </c>
       <c r="L22">
-        <v>3118.696785660024</v>
+        <v>3090.301067412581</v>
       </c>
       <c r="M22">
-        <v>2826.519117362694</v>
+        <v>2811.830530895172</v>
       </c>
       <c r="N22">
-        <v>1128.885371383932</v>
+        <v>1126.459166284534</v>
       </c>
       <c r="O22">
-        <v>616.2235557677528</v>
+        <v>612.7328956484231</v>
       </c>
       <c r="P22">
-        <v>56.70726118342905</v>
+        <v>58.53624533488201</v>
       </c>
       <c r="Q22">
         <v>0.008253024506255816</v>
       </c>
       <c r="S22">
-        <v>51.26614119043931</v>
+        <v>51.72724217157731</v>
       </c>
       <c r="T22">
-        <v>90.11703068245085</v>
+        <v>90.80547942802319</v>
       </c>
       <c r="U22">
-        <v>78.94122161162456</v>
+        <v>78.56350057518092</v>
       </c>
       <c r="V22">
-        <v>205.7243870562696</v>
+        <v>206.4421573477693</v>
       </c>
       <c r="W22">
-        <v>261.1749940655035</v>
+        <v>261.7122643560871</v>
       </c>
       <c r="Z22">
-        <v>0.2237793079500502</v>
+        <v>0.2303610523015193</v>
       </c>
       <c r="AA22">
-        <v>39.04091865516931</v>
+        <v>39.65363215010155</v>
       </c>
       <c r="AB22">
-        <v>64.39862720807693</v>
+        <v>64.82563870807076</v>
       </c>
       <c r="AC22">
         <v>-6.780048395757842E-16</v>
@@ -3308,43 +3311,43 @@
         <v>0.003866172025281671</v>
       </c>
       <c r="AH22">
-        <v>2020.530226206849</v>
+        <v>1993.461933718553</v>
       </c>
       <c r="AJ22">
-        <v>70.72421068193752</v>
+        <v>70.98041452584262</v>
       </c>
       <c r="AK22">
-        <v>727.4089620270735</v>
+        <v>723.435750770343</v>
       </c>
       <c r="AL22">
-        <v>97.20628525213442</v>
+        <v>97.19788777641067</v>
       </c>
       <c r="AM22">
-        <v>33.45768866685519</v>
+        <v>34.08011148289355</v>
       </c>
       <c r="AN22">
-        <v>29.53502989482972</v>
+        <v>29.30649972566236</v>
       </c>
       <c r="AO22">
-        <v>142.9005968878484</v>
+        <v>144.9924563520914</v>
       </c>
       <c r="AP22">
-        <v>2220.108124250088</v>
+        <v>2203.386024288404</v>
       </c>
       <c r="AQ22">
-        <v>155.8752219650086</v>
+        <v>158.2707718758985</v>
       </c>
       <c r="AR22">
-        <v>101.3360090896537</v>
+        <v>103.2414844899323</v>
       </c>
       <c r="AS22">
-        <v>15.85880390133695</v>
+        <v>15.07414512268055</v>
       </c>
       <c r="AT22">
         <v>8.307309736927188</v>
       </c>
       <c r="AU22">
-        <v>344.1304223055339</v>
+        <v>342.9690113702616</v>
       </c>
       <c r="AV22">
         <v>1</v>
@@ -3357,22 +3360,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>446.0969372552447</v>
+        <v>448.0110245262171</v>
       </c>
       <c r="C23">
         <v>55.02805657459191</v>
       </c>
       <c r="D23">
-        <v>5529.019267295256</v>
+        <v>5484.272843800647</v>
       </c>
       <c r="E23">
-        <v>210.6185484945813</v>
+        <v>203.7556245673298</v>
       </c>
       <c r="F23">
-        <v>425.5109191870501</v>
+        <v>428.2184211641384</v>
       </c>
       <c r="G23">
-        <v>12.97163407599636</v>
+        <v>12.68584496936034</v>
       </c>
       <c r="H23">
         <v>35.5337919635917</v>
@@ -3387,22 +3390,22 @@
         <v>-1.534692806646624E-14</v>
       </c>
       <c r="L23">
-        <v>2376.981280868997</v>
+        <v>2364.538151498577</v>
       </c>
       <c r="M23">
-        <v>1414.60821062782</v>
+        <v>1421.860888329588</v>
       </c>
       <c r="N23">
-        <v>1737.429775798439</v>
+        <v>1697.873803972481</v>
       </c>
       <c r="O23">
-        <v>187.8273661519494</v>
+        <v>180.1398701073066</v>
       </c>
       <c r="P23">
         <v>5.311899241145852</v>
       </c>
       <c r="S23">
-        <v>21.65291821952906</v>
+        <v>22.55337461179395</v>
       </c>
       <c r="T23">
         <v>28.22869560084434</v>
@@ -3411,16 +3414,16 @@
         <v>28.2061757746862</v>
       </c>
       <c r="V23">
-        <v>271.906414406621</v>
+        <v>276.0921946975892</v>
       </c>
       <c r="W23">
-        <v>111.2807640872981</v>
+        <v>112.6240684862937</v>
       </c>
       <c r="Z23">
         <v>-5.404360319086195E-15</v>
       </c>
       <c r="AA23">
-        <v>8.022424370274603</v>
+        <v>8.066582577353367</v>
       </c>
       <c r="AB23">
         <v>6.298994170918602</v>
@@ -3432,31 +3435,31 @@
         <v>35.5337919635917</v>
       </c>
       <c r="AH23">
-        <v>827.3215843223403</v>
+        <v>832.1582771525897</v>
       </c>
       <c r="AJ23">
-        <v>14.86381783488562</v>
+        <v>14.91657053574726</v>
       </c>
       <c r="AK23">
-        <v>927.2558737556816</v>
+        <v>939.6030134876868</v>
       </c>
       <c r="AL23">
-        <v>148.4808812787591</v>
+        <v>143.6661414138005</v>
       </c>
       <c r="AM23">
         <v>158.2912504035421</v>
       </c>
       <c r="AN23">
-        <v>44.89798885487215</v>
+        <v>47.3099964492415</v>
       </c>
       <c r="AO23">
-        <v>267.1764023048837</v>
+        <v>249.6984021097753</v>
       </c>
       <c r="AP23">
-        <v>994.9714693350694</v>
+        <v>1009.779811536662</v>
       </c>
       <c r="AQ23">
-        <v>24.82363208729171</v>
+        <v>24.27794140953907</v>
       </c>
       <c r="AR23">
         <v>36.27266159715779</v>
@@ -3465,7 +3468,7 @@
         <v>3.814679993240846</v>
       </c>
       <c r="AU23">
-        <v>357.9954933235524</v>
+        <v>353.4400272269403</v>
       </c>
       <c r="AV23">
         <v>1</v>
@@ -3538,13 +3541,13 @@
         <v>118.6791181789837</v>
       </c>
       <c r="V24">
-        <v>286.59643872676</v>
+        <v>286.6021725879388</v>
       </c>
       <c r="W24">
         <v>295.660349998362</v>
       </c>
       <c r="Z24">
-        <v>11.53075280218674</v>
+        <v>11.55518601954596</v>
       </c>
       <c r="AA24">
         <v>28.4164441912733</v>
@@ -3580,13 +3583,13 @@
         <v>94.83243992128801</v>
       </c>
       <c r="AM24">
-        <v>33.7382465974739</v>
+        <v>33.7608782218186</v>
       </c>
       <c r="AN24">
         <v>42.38932308482197</v>
       </c>
       <c r="AO24">
-        <v>117.7642929183138</v>
+        <v>117.8134156896769</v>
       </c>
       <c r="AP24">
         <v>2082.635292275251</v>
@@ -3617,22 +3620,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>1185.975139882347</v>
+        <v>1184.134297819028</v>
       </c>
       <c r="C25">
-        <v>165.3536995975672</v>
+        <v>165.0746345008095</v>
       </c>
       <c r="D25">
-        <v>8052.512660768194</v>
+        <v>8046.054103530919</v>
       </c>
       <c r="E25">
-        <v>628.2266148979086</v>
+        <v>626.6054700060693</v>
       </c>
       <c r="F25">
-        <v>1031.684811423651</v>
+        <v>1029.813166458684</v>
       </c>
       <c r="G25">
-        <v>149.667359376649</v>
+        <v>149.713940329771</v>
       </c>
       <c r="H25">
         <v>11.24922476631554</v>
@@ -3641,25 +3644,25 @@
         <v>284.5425322954725</v>
       </c>
       <c r="J25">
-        <v>87.78141138391265</v>
+        <v>87.77355057879316</v>
       </c>
       <c r="K25">
         <v>0.03262569226268733</v>
       </c>
       <c r="L25">
-        <v>3946.699950051145</v>
+        <v>3942.35997656567</v>
       </c>
       <c r="M25">
-        <v>2997.846412343469</v>
+        <v>2995.846747050983</v>
       </c>
       <c r="N25">
-        <v>1107.96629837358</v>
+        <v>1107.847379914266</v>
       </c>
       <c r="O25">
-        <v>423.7902834347027</v>
+        <v>422.7933795762269</v>
       </c>
       <c r="P25">
-        <v>132.3860006694533</v>
+        <v>131.880068509667</v>
       </c>
       <c r="Q25">
         <v>13.81041950298377</v>
@@ -3668,28 +3671,28 @@
         <v>18.52253699785579</v>
       </c>
       <c r="S25">
-        <v>83.5141908031876</v>
+        <v>83.3015007380657</v>
       </c>
       <c r="T25">
-        <v>203.2261135273958</v>
+        <v>202.887858995886</v>
       </c>
       <c r="U25">
-        <v>142.430404408459</v>
+        <v>142.1005846662375</v>
       </c>
       <c r="V25">
-        <v>377.7177322923181</v>
+        <v>377.038215543511</v>
       </c>
       <c r="W25">
-        <v>306.1574459287075</v>
+        <v>305.6384213327573</v>
       </c>
       <c r="Z25">
-        <v>4.838593222063728</v>
+        <v>4.815442058321796</v>
       </c>
       <c r="AA25">
-        <v>61.84616857746305</v>
+        <v>61.87217304459266</v>
       </c>
       <c r="AB25">
-        <v>89.35117670161077</v>
+        <v>89.36679796721268</v>
       </c>
       <c r="AC25">
         <v>5.56169388497354E-16</v>
@@ -3707,43 +3710,43 @@
         <v>6.250202025130831</v>
       </c>
       <c r="AH25">
-        <v>3076.223155479389</v>
+        <v>3071.865262624635</v>
       </c>
       <c r="AJ25">
-        <v>134.4843852240486</v>
+        <v>134.2920618085394</v>
       </c>
       <c r="AK25">
-        <v>470.5815193102653</v>
+        <v>470.7848577217045</v>
       </c>
       <c r="AL25">
-        <v>100.815466367737</v>
+        <v>100.846047675846</v>
       </c>
       <c r="AM25">
-        <v>43.83680646404046</v>
+        <v>43.99532599792018</v>
       </c>
       <c r="AN25">
-        <v>25.8769836765678</v>
+        <v>25.84772365500317</v>
       </c>
       <c r="AO25">
-        <v>101.0958001823152</v>
+        <v>100.9362003077183</v>
       </c>
       <c r="AP25">
-        <v>2446.704979485154</v>
+        <v>2444.117082995439</v>
       </c>
       <c r="AQ25">
-        <v>251.0161228042938</v>
+        <v>251.1967747682377</v>
       </c>
       <c r="AR25">
         <v>64.49406439242074</v>
       </c>
       <c r="AS25">
-        <v>23.45149507581805</v>
+        <v>23.41495980732754</v>
       </c>
       <c r="AT25">
         <v>100.4752440462378</v>
       </c>
       <c r="AU25">
-        <v>212.1841155378953</v>
+        <v>212.8458375279655</v>
       </c>
       <c r="AV25">
         <v>1</v>
@@ -3874,88 +3877,88 @@
         </is>
       </c>
       <c r="B27">
-        <v>1244.898524040178</v>
+        <v>1245.3730927943</v>
       </c>
       <c r="C27">
-        <v>181.0698426290762</v>
+        <v>181.549231006088</v>
       </c>
       <c r="D27">
-        <v>7319.693410738366</v>
+        <v>7316.662771343364</v>
       </c>
       <c r="E27">
-        <v>466.6588257423832</v>
+        <v>470.3852836293678</v>
       </c>
       <c r="F27">
-        <v>1146.277901053154</v>
+        <v>1146.768558356453</v>
       </c>
       <c r="G27">
-        <v>94.87679437346125</v>
+        <v>94.86617402099348</v>
       </c>
       <c r="H27">
-        <v>11.45817579663863</v>
+        <v>11.408633196749</v>
       </c>
       <c r="I27">
-        <v>246.3608178040394</v>
+        <v>246.7315119035978</v>
       </c>
       <c r="J27">
-        <v>67.35573116882203</v>
+        <v>67.40820812024289</v>
       </c>
       <c r="K27">
-        <v>3.598857806089743</v>
+        <v>3.578801804355434</v>
       </c>
       <c r="L27">
-        <v>3805.078020734939</v>
+        <v>3802.8211980764</v>
       </c>
       <c r="M27">
-        <v>2616.739727527851</v>
+        <v>2615.364891207917</v>
       </c>
       <c r="N27">
-        <v>903.513814202267</v>
+        <v>904.1097647051849</v>
       </c>
       <c r="O27">
-        <v>221.0422506187614</v>
+        <v>221.3776424039823</v>
       </c>
       <c r="P27">
-        <v>175.0872837220563</v>
+        <v>178.8571257904589</v>
       </c>
       <c r="Q27">
-        <v>4.344172116676698</v>
+        <v>4.121532129884597</v>
       </c>
       <c r="R27">
         <v>1.181639278571671</v>
       </c>
       <c r="S27">
-        <v>111.677181273829</v>
+        <v>112.1190767248769</v>
       </c>
       <c r="T27">
-        <v>328.659353635851</v>
+        <v>329.2061332748553</v>
       </c>
       <c r="U27">
-        <v>130.6201284162451</v>
+        <v>130.5296509255306</v>
       </c>
       <c r="V27">
-        <v>433.3149149886308</v>
+        <v>433.1600546107289</v>
       </c>
       <c r="W27">
-        <v>250.3859969833492</v>
+        <v>250.580839987946</v>
       </c>
       <c r="Z27">
-        <v>6.897887561756233</v>
+        <v>6.884388760265517</v>
       </c>
       <c r="AA27">
-        <v>36.84390563785018</v>
+        <v>36.90388055943028</v>
       </c>
       <c r="AB27">
-        <v>64.63179203119371</v>
+        <v>64.54770993811503</v>
       </c>
       <c r="AC27">
-        <v>1.940878656104455E-15</v>
+        <v>1.923245187466605E-15</v>
       </c>
       <c r="AD27">
         <v>1.665238684124251</v>
       </c>
       <c r="AE27">
-        <v>6.722916150199974</v>
+        <v>6.42696567163148</v>
       </c>
       <c r="AF27">
         <v>38.82408039984279</v>
@@ -3964,43 +3967,43 @@
         <v>3.106879656265534</v>
       </c>
       <c r="AH27">
-        <v>2998.851743120937</v>
+        <v>2996.402161720726</v>
       </c>
       <c r="AJ27">
-        <v>142.7605467522664</v>
+        <v>142.6297175059317</v>
       </c>
       <c r="AK27">
-        <v>439.8035641949485</v>
+        <v>440.2532770921396</v>
       </c>
       <c r="AL27">
-        <v>95.20716810786905</v>
+        <v>95.22992280181495</v>
       </c>
       <c r="AM27">
-        <v>23.95661283019205</v>
+        <v>23.9107063043517</v>
       </c>
       <c r="AN27">
         <v>25.68708160030294</v>
       </c>
       <c r="AO27">
-        <v>95.8134588256803</v>
+        <v>95.70747259112501</v>
       </c>
       <c r="AP27">
-        <v>1973.872967156138</v>
+        <v>1972.407713433833</v>
       </c>
       <c r="AQ27">
-        <v>276.5120476183987</v>
+        <v>276.6479607396732</v>
       </c>
       <c r="AR27">
-        <v>155.8442723102716</v>
+        <v>156.077922977693</v>
       </c>
       <c r="AS27">
-        <v>21.22963937358354</v>
+        <v>21.2224224585041</v>
       </c>
       <c r="AT27">
-        <v>12.39953680262162</v>
+        <v>12.37550527061049</v>
       </c>
       <c r="AU27">
-        <v>216.4061125885461</v>
+        <v>216.1333938911839</v>
       </c>
       <c r="AV27">
         <v>1</v>
@@ -4013,127 +4016,127 @@
         </is>
       </c>
       <c r="B28">
-        <v>574.5826298785489</v>
+        <v>590.1392828649523</v>
       </c>
       <c r="C28">
-        <v>111.4465119473491</v>
+        <v>128.6697474574575</v>
       </c>
       <c r="D28">
-        <v>8944.189999122507</v>
+        <v>9018.772719434084</v>
       </c>
       <c r="E28">
-        <v>222.3298463493575</v>
+        <v>225.8900962827426</v>
       </c>
       <c r="F28">
-        <v>549.8190856395711</v>
+        <v>565.0249303528935</v>
       </c>
       <c r="G28">
-        <v>23.18032951096759</v>
+        <v>23.36501801096198</v>
       </c>
       <c r="H28">
-        <v>19.4148161937559</v>
+        <v>20.45513201174031</v>
       </c>
       <c r="I28">
-        <v>189.4619670744927</v>
+        <v>218.7837798236315</v>
       </c>
       <c r="J28">
-        <v>36.99272281013427</v>
+        <v>37.4088882532572</v>
       </c>
       <c r="K28">
-        <v>5.938240872175045E-16</v>
+        <v>-2.032684762109858E-15</v>
       </c>
       <c r="L28">
-        <v>5410.532540475614</v>
+        <v>5487.877562300815</v>
       </c>
       <c r="M28">
-        <v>2024.349385696395</v>
+        <v>2014.89510838376</v>
       </c>
       <c r="N28">
-        <v>1509.3080729505</v>
+        <v>1516.000048749509</v>
       </c>
       <c r="O28">
-        <v>176.7440237823293</v>
+        <v>181.4743183838059</v>
       </c>
       <c r="P28">
-        <v>121.9699687481536</v>
+        <v>119.4817703363299</v>
       </c>
       <c r="Q28">
         <v>12.98147891380372</v>
       </c>
       <c r="S28">
-        <v>16.64739873202118</v>
+        <v>17.0953063803689</v>
       </c>
       <c r="T28">
-        <v>31.09801125573763</v>
+        <v>30.4193006503568</v>
       </c>
       <c r="U28">
-        <v>138.720797826301</v>
+        <v>149.1519420489016</v>
       </c>
       <c r="V28">
-        <v>240.9143864976693</v>
+        <v>247.8741477017943</v>
       </c>
       <c r="W28">
-        <v>142.622316941001</v>
+        <v>141.4994367350842</v>
       </c>
       <c r="Z28">
-        <v>1.43865203555422</v>
+        <v>1.388005391369795</v>
       </c>
       <c r="AA28">
-        <v>11.68583297042613</v>
+        <v>12.09641557148219</v>
       </c>
       <c r="AB28">
-        <v>13.40846870199749</v>
+        <v>13.05068008438368</v>
       </c>
       <c r="AC28">
-        <v>-1.877822842173898E-16</v>
+        <v>-7.264296627983323E-17</v>
       </c>
       <c r="AD28">
         <v>0.0008327328758771298</v>
       </c>
       <c r="AF28">
-        <v>21.76116461561307</v>
+        <v>22.94108926821906</v>
       </c>
       <c r="AG28">
         <v>9.90045019597234</v>
       </c>
       <c r="AH28">
-        <v>3744.676932244915</v>
+        <v>3789.809612653155</v>
       </c>
       <c r="AJ28">
-        <v>117.8920314325084</v>
+        <v>131.2836673204265</v>
       </c>
       <c r="AK28">
-        <v>1038.05974743105</v>
+        <v>1055.592282255554</v>
       </c>
       <c r="AL28">
-        <v>133.7038538435976</v>
+        <v>133.406045833899</v>
       </c>
       <c r="AM28">
-        <v>100.8427847720346</v>
+        <v>101.4933506620098</v>
       </c>
       <c r="AN28">
-        <v>56.59246246868586</v>
+        <v>56.97863551462265</v>
       </c>
       <c r="AO28">
-        <v>222.8640284768074</v>
+        <v>224.0217258212939</v>
       </c>
       <c r="AP28">
-        <v>1470.967783569237</v>
+        <v>1460.001717808222</v>
       </c>
       <c r="AQ28">
-        <v>96.58857595687546</v>
+        <v>95.99107076467398</v>
       </c>
       <c r="AR28">
-        <v>49.70543151065699</v>
+        <v>48.39329004880209</v>
       </c>
       <c r="AS28">
-        <v>8.822803441543471</v>
+        <v>8.907679221026751</v>
       </c>
       <c r="AT28">
         <v>46.91916992302737</v>
       </c>
       <c r="AU28">
-        <v>410.4816819067848</v>
+        <v>414.313043194131</v>
       </c>
       <c r="AV28">
         <v>1</v>
